--- a/public/data/participant.xlsx
+++ b/public/data/participant.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="834">
   <si>
     <t>No.</t>
   </si>
@@ -2333,9 +2333,6 @@
     <t>Indah Asri Suherman</t>
   </si>
   <si>
-    <t>Relay</t>
-  </si>
-  <si>
     <t>Relay USS Running Rangers Merah</t>
   </si>
   <si>
@@ -2355,6 +2352,180 @@
   </si>
   <si>
     <t>Relay - Relay Anti Kendor</t>
+  </si>
+  <si>
+    <t>Relay - Swift</t>
+  </si>
+  <si>
+    <t>Relay - BIASA BIASA AJA</t>
+  </si>
+  <si>
+    <t>Relay - KMM RUNNERS</t>
+  </si>
+  <si>
+    <t>Relay - OPER DERITA</t>
+  </si>
+  <si>
+    <t>Relay - Hana Run Team B</t>
+  </si>
+  <si>
+    <t>Relay - Bintang Kejora</t>
+  </si>
+  <si>
+    <t>Relay - Hamba Allah</t>
+  </si>
+  <si>
+    <t>Relay - NGACIR SQUAD</t>
+  </si>
+  <si>
+    <t>Relay - THE RAIDERS</t>
+  </si>
+  <si>
+    <t>Relay - TBL Squad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay - Dazzling lab </t>
+  </si>
+  <si>
+    <t>Relay - HURU HARA</t>
+  </si>
+  <si>
+    <t>Relay - SEKEDAR C</t>
+  </si>
+  <si>
+    <t>Relay - CSR Team 7 Happy</t>
+  </si>
+  <si>
+    <t>Relay - Senang Senang</t>
+  </si>
+  <si>
+    <t>Relay - RGRDS</t>
+  </si>
+  <si>
+    <t>Relay - Run &amp; Done</t>
+  </si>
+  <si>
+    <t>Relay - Pelarian #4</t>
+  </si>
+  <si>
+    <t>Relay - Slow Division</t>
+  </si>
+  <si>
+    <t>Relay - M4 PRO 512 GB</t>
+  </si>
+  <si>
+    <t>Relay - Sekedar A</t>
+  </si>
+  <si>
+    <t>Relay - SEKEDAR B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay - TUPAI ACADEMY TEAM 1 </t>
+  </si>
+  <si>
+    <t>Relay - Pelari Kalcer</t>
+  </si>
+  <si>
+    <t>Relay - Vine Run</t>
+  </si>
+  <si>
+    <t>Relay - PGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay - ABLA ABLA </t>
+  </si>
+  <si>
+    <t>Relay - THE SUTRISNOS</t>
+  </si>
+  <si>
+    <t>Relay - Maharama Runners 2</t>
+  </si>
+  <si>
+    <t>Relay - The Flash</t>
+  </si>
+  <si>
+    <t>Relay - Fast Five</t>
+  </si>
+  <si>
+    <t>Relay - Endorphive</t>
+  </si>
+  <si>
+    <t>Relay - JAMAEL X CSR</t>
+  </si>
+  <si>
+    <t>Relay - CrowdStrike</t>
+  </si>
+  <si>
+    <t>Relay - Mazenta Runners</t>
+  </si>
+  <si>
+    <t>Relay - BINLUV</t>
+  </si>
+  <si>
+    <t>Relay - peLARIan 01</t>
+  </si>
+  <si>
+    <t>Relay - Balap Batu</t>
+  </si>
+  <si>
+    <t>Relay - DitNavPen</t>
+  </si>
+  <si>
+    <t>Relay - Ciledug Stride Run (Team 5)</t>
+  </si>
+  <si>
+    <t>Relay - bicer</t>
+  </si>
+  <si>
+    <t>Relay - At/Lite</t>
+  </si>
+  <si>
+    <t>Relay - Mayapad Runner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relay - Cewe Centyl </t>
+  </si>
+  <si>
+    <t>Relay - dialagi dialagi</t>
+  </si>
+  <si>
+    <t>Relay - Team Asyikkk</t>
+  </si>
+  <si>
+    <t>Relay - Ciledug Stride Monster 9</t>
+  </si>
+  <si>
+    <t>Relay - GLC ONE SPIRIT RELAY</t>
+  </si>
+  <si>
+    <t>Relay - PEMANCING HANDAL</t>
+  </si>
+  <si>
+    <t>Relay - Ciledug Stride Run T1</t>
+  </si>
+  <si>
+    <t>Relay - Pace Collective</t>
+  </si>
+  <si>
+    <t>Relay - AFTER 7 CLUB</t>
+  </si>
+  <si>
+    <t>Relay - TBC (Tawaf Bintaro Club)</t>
+  </si>
+  <si>
+    <t>Relay - TEAM REJO</t>
+  </si>
+  <si>
+    <t>Relay - RundayMates #1</t>
+  </si>
+  <si>
+    <t>Relay - Lari-larian</t>
+  </si>
+  <si>
+    <t>Relay - -341</t>
+  </si>
+  <si>
+    <t>Relay - CSR Relay-4</t>
   </si>
 </sst>
 </file>
@@ -7815,7 +7986,7 @@
         <v>441</v>
       </c>
       <c r="D445" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="446" spans="2:4" x14ac:dyDescent="0.35">
@@ -7826,7 +7997,7 @@
         <v>449</v>
       </c>
       <c r="D446" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="447" spans="2:4" x14ac:dyDescent="0.35">
@@ -7837,7 +8008,7 @@
         <v>450</v>
       </c>
       <c r="D447" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="448" spans="2:4" x14ac:dyDescent="0.35">
@@ -7848,7 +8019,7 @@
         <v>451</v>
       </c>
       <c r="D448" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="449" spans="2:4" x14ac:dyDescent="0.35">
@@ -7859,7 +8030,7 @@
         <v>452</v>
       </c>
       <c r="D449" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="450" spans="2:4" x14ac:dyDescent="0.35">
@@ -7870,7 +8041,7 @@
         <v>453</v>
       </c>
       <c r="D450" s="11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="451" spans="2:4" x14ac:dyDescent="0.35">
@@ -7881,7 +8052,7 @@
         <v>454</v>
       </c>
       <c r="D451" s="11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="452" spans="2:4" x14ac:dyDescent="0.35">
@@ -7892,7 +8063,7 @@
         <v>455</v>
       </c>
       <c r="D452" s="11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="453" spans="2:4" x14ac:dyDescent="0.35">
@@ -7903,7 +8074,7 @@
         <v>456</v>
       </c>
       <c r="D453" s="11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="454" spans="2:4" x14ac:dyDescent="0.35">
@@ -7914,7 +8085,7 @@
         <v>457</v>
       </c>
       <c r="D454" s="11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="455" spans="2:4" x14ac:dyDescent="0.35">
@@ -7925,7 +8096,7 @@
         <v>458</v>
       </c>
       <c r="D455" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="456" spans="2:4" x14ac:dyDescent="0.35">
@@ -7936,7 +8107,7 @@
         <v>459</v>
       </c>
       <c r="D456" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="457" spans="2:4" x14ac:dyDescent="0.35">
@@ -7947,7 +8118,7 @@
         <v>460</v>
       </c>
       <c r="D457" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="458" spans="2:4" x14ac:dyDescent="0.35">
@@ -7958,7 +8129,7 @@
         <v>461</v>
       </c>
       <c r="D458" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="459" spans="2:4" x14ac:dyDescent="0.35">
@@ -7969,7 +8140,7 @@
         <v>462</v>
       </c>
       <c r="D459" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="460" spans="2:4" x14ac:dyDescent="0.35">
@@ -7980,7 +8151,7 @@
         <v>463</v>
       </c>
       <c r="D460" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="461" spans="2:4" x14ac:dyDescent="0.35">
@@ -7991,7 +8162,7 @@
         <v>464</v>
       </c>
       <c r="D461" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="462" spans="2:4" x14ac:dyDescent="0.35">
@@ -8002,7 +8173,7 @@
         <v>465</v>
       </c>
       <c r="D462" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="463" spans="2:4" x14ac:dyDescent="0.35">
@@ -8013,7 +8184,7 @@
         <v>466</v>
       </c>
       <c r="D463" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="464" spans="2:4" x14ac:dyDescent="0.35">
@@ -8024,7 +8195,7 @@
         <v>467</v>
       </c>
       <c r="D464" s="11" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="465" spans="2:4" x14ac:dyDescent="0.35">
@@ -8035,7 +8206,7 @@
         <v>468</v>
       </c>
       <c r="D465" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="466" spans="2:4" x14ac:dyDescent="0.35">
@@ -8046,7 +8217,7 @@
         <v>469</v>
       </c>
       <c r="D466" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="467" spans="2:4" x14ac:dyDescent="0.35">
@@ -8057,7 +8228,7 @@
         <v>470</v>
       </c>
       <c r="D467" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="468" spans="2:4" x14ac:dyDescent="0.35">
@@ -8068,7 +8239,7 @@
         <v>471</v>
       </c>
       <c r="D468" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="469" spans="2:4" x14ac:dyDescent="0.35">
@@ -8079,7 +8250,7 @@
         <v>472</v>
       </c>
       <c r="D469" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="470" spans="2:4" x14ac:dyDescent="0.35">
@@ -8090,7 +8261,7 @@
         <v>473</v>
       </c>
       <c r="D470" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="471" spans="2:4" x14ac:dyDescent="0.35">
@@ -8101,7 +8272,7 @@
         <v>474</v>
       </c>
       <c r="D471" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="472" spans="2:4" x14ac:dyDescent="0.35">
@@ -8112,7 +8283,7 @@
         <v>475</v>
       </c>
       <c r="D472" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="473" spans="2:4" x14ac:dyDescent="0.35">
@@ -8123,7 +8294,7 @@
         <v>476</v>
       </c>
       <c r="D473" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="474" spans="2:4" x14ac:dyDescent="0.35">
@@ -8134,7 +8305,7 @@
         <v>477</v>
       </c>
       <c r="D474" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="475" spans="2:4" x14ac:dyDescent="0.35">
@@ -8145,7 +8316,7 @@
         <v>478</v>
       </c>
       <c r="D475" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="476" spans="2:4" x14ac:dyDescent="0.35">
@@ -8156,7 +8327,7 @@
         <v>479</v>
       </c>
       <c r="D476" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="477" spans="2:4" x14ac:dyDescent="0.35">
@@ -8167,7 +8338,7 @@
         <v>480</v>
       </c>
       <c r="D477" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="478" spans="2:4" x14ac:dyDescent="0.35">
@@ -8178,7 +8349,7 @@
         <v>481</v>
       </c>
       <c r="D478" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="479" spans="2:4" x14ac:dyDescent="0.35">
@@ -8189,7 +8360,7 @@
         <v>482</v>
       </c>
       <c r="D479" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="480" spans="2:4" x14ac:dyDescent="0.35">
@@ -8200,7 +8371,7 @@
         <v>483</v>
       </c>
       <c r="D480" s="11" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="481" spans="2:4" x14ac:dyDescent="0.35">
@@ -8211,7 +8382,7 @@
         <v>484</v>
       </c>
       <c r="D481" s="11" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="482" spans="2:4" x14ac:dyDescent="0.35">
@@ -8222,7 +8393,7 @@
         <v>485</v>
       </c>
       <c r="D482" s="11" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="483" spans="2:4" x14ac:dyDescent="0.35">
@@ -8233,7 +8404,7 @@
         <v>486</v>
       </c>
       <c r="D483" s="11" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="484" spans="2:4" x14ac:dyDescent="0.35">
@@ -8244,7 +8415,7 @@
         <v>487</v>
       </c>
       <c r="D484" s="11" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="485" spans="2:4" x14ac:dyDescent="0.35">
@@ -8255,7 +8426,7 @@
         <v>488</v>
       </c>
       <c r="D485" s="11" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="486" spans="2:4" x14ac:dyDescent="0.35">
@@ -8266,7 +8437,7 @@
         <v>489</v>
       </c>
       <c r="D486" s="11" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="487" spans="2:4" x14ac:dyDescent="0.35">
@@ -8277,7 +8448,7 @@
         <v>490</v>
       </c>
       <c r="D487" s="11" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="488" spans="2:4" x14ac:dyDescent="0.35">
@@ -8288,7 +8459,7 @@
         <v>491</v>
       </c>
       <c r="D488" s="11" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="489" spans="2:4" x14ac:dyDescent="0.35">
@@ -8299,7 +8470,7 @@
         <v>492</v>
       </c>
       <c r="D489" s="11" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
     </row>
     <row r="490" spans="2:4" x14ac:dyDescent="0.35">
@@ -8310,7 +8481,7 @@
         <v>493</v>
       </c>
       <c r="D490" s="11" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
     </row>
     <row r="491" spans="2:4" x14ac:dyDescent="0.35">
@@ -8321,7 +8492,7 @@
         <v>494</v>
       </c>
       <c r="D491" s="11" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
     </row>
     <row r="492" spans="2:4" x14ac:dyDescent="0.35">
@@ -8332,7 +8503,7 @@
         <v>495</v>
       </c>
       <c r="D492" s="11" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
     </row>
     <row r="493" spans="2:4" x14ac:dyDescent="0.35">
@@ -8343,7 +8514,7 @@
         <v>496</v>
       </c>
       <c r="D493" s="11" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
     </row>
     <row r="494" spans="2:4" x14ac:dyDescent="0.35">
@@ -8354,7 +8525,7 @@
         <v>497</v>
       </c>
       <c r="D494" s="11" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
     </row>
     <row r="495" spans="2:4" x14ac:dyDescent="0.35">
@@ -8365,7 +8536,7 @@
         <v>498</v>
       </c>
       <c r="D495" s="11" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
     </row>
     <row r="496" spans="2:4" x14ac:dyDescent="0.35">
@@ -8376,7 +8547,7 @@
         <v>499</v>
       </c>
       <c r="D496" s="11" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
     </row>
     <row r="497" spans="2:4" x14ac:dyDescent="0.35">
@@ -8387,7 +8558,7 @@
         <v>500</v>
       </c>
       <c r="D497" s="11" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
     </row>
     <row r="498" spans="2:4" x14ac:dyDescent="0.35">
@@ -8398,7 +8569,7 @@
         <v>501</v>
       </c>
       <c r="D498" s="11" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
     </row>
     <row r="499" spans="2:4" x14ac:dyDescent="0.35">
@@ -8409,7 +8580,7 @@
         <v>502</v>
       </c>
       <c r="D499" s="11" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
     </row>
     <row r="500" spans="2:4" x14ac:dyDescent="0.35">
@@ -8420,7 +8591,7 @@
         <v>503</v>
       </c>
       <c r="D500" s="11" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
     <row r="501" spans="2:4" x14ac:dyDescent="0.35">
@@ -8431,7 +8602,7 @@
         <v>504</v>
       </c>
       <c r="D501" s="11" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
     <row r="502" spans="2:4" x14ac:dyDescent="0.35">
@@ -8442,7 +8613,7 @@
         <v>505</v>
       </c>
       <c r="D502" s="11" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
     <row r="503" spans="2:4" x14ac:dyDescent="0.35">
@@ -8453,7 +8624,7 @@
         <v>506</v>
       </c>
       <c r="D503" s="11" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
     <row r="504" spans="2:4" x14ac:dyDescent="0.35">
@@ -8464,7 +8635,7 @@
         <v>507</v>
       </c>
       <c r="D504" s="11" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
     <row r="505" spans="2:4" x14ac:dyDescent="0.35">
@@ -8475,7 +8646,7 @@
         <v>508</v>
       </c>
       <c r="D505" s="11" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="506" spans="2:4" x14ac:dyDescent="0.35">
@@ -8486,7 +8657,7 @@
         <v>509</v>
       </c>
       <c r="D506" s="11" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="507" spans="2:4" x14ac:dyDescent="0.35">
@@ -8497,7 +8668,7 @@
         <v>510</v>
       </c>
       <c r="D507" s="11" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="508" spans="2:4" x14ac:dyDescent="0.35">
@@ -8508,7 +8679,7 @@
         <v>511</v>
       </c>
       <c r="D508" s="11" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="509" spans="2:4" x14ac:dyDescent="0.35">
@@ -8519,7 +8690,7 @@
         <v>512</v>
       </c>
       <c r="D509" s="11" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
     </row>
     <row r="510" spans="2:4" x14ac:dyDescent="0.35">
@@ -8530,7 +8701,7 @@
         <v>513</v>
       </c>
       <c r="D510" s="11" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
     </row>
     <row r="511" spans="2:4" x14ac:dyDescent="0.35">
@@ -8541,7 +8712,7 @@
         <v>514</v>
       </c>
       <c r="D511" s="11" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
     </row>
     <row r="512" spans="2:4" x14ac:dyDescent="0.35">
@@ -8552,7 +8723,7 @@
         <v>515</v>
       </c>
       <c r="D512" s="11" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
     </row>
     <row r="513" spans="2:4" x14ac:dyDescent="0.35">
@@ -8563,7 +8734,7 @@
         <v>516</v>
       </c>
       <c r="D513" s="11" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
     </row>
     <row r="514" spans="2:4" x14ac:dyDescent="0.35">
@@ -8574,7 +8745,7 @@
         <v>517</v>
       </c>
       <c r="D514" s="11" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
     </row>
     <row r="515" spans="2:4" x14ac:dyDescent="0.35">
@@ -8585,7 +8756,7 @@
         <v>518</v>
       </c>
       <c r="D515" s="11" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="516" spans="2:4" x14ac:dyDescent="0.35">
@@ -8596,7 +8767,7 @@
         <v>519</v>
       </c>
       <c r="D516" s="11" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="517" spans="2:4" x14ac:dyDescent="0.35">
@@ -8607,7 +8778,7 @@
         <v>520</v>
       </c>
       <c r="D517" s="11" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="518" spans="2:4" x14ac:dyDescent="0.35">
@@ -8618,7 +8789,7 @@
         <v>521</v>
       </c>
       <c r="D518" s="11" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="519" spans="2:4" x14ac:dyDescent="0.35">
@@ -8629,7 +8800,7 @@
         <v>522</v>
       </c>
       <c r="D519" s="11" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="520" spans="2:4" x14ac:dyDescent="0.35">
@@ -8640,7 +8811,7 @@
         <v>523</v>
       </c>
       <c r="D520" s="11" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
     </row>
     <row r="521" spans="2:4" x14ac:dyDescent="0.35">
@@ -8651,7 +8822,7 @@
         <v>524</v>
       </c>
       <c r="D521" s="11" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
     </row>
     <row r="522" spans="2:4" x14ac:dyDescent="0.35">
@@ -8662,7 +8833,7 @@
         <v>525</v>
       </c>
       <c r="D522" s="11" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
     </row>
     <row r="523" spans="2:4" x14ac:dyDescent="0.35">
@@ -8673,7 +8844,7 @@
         <v>526</v>
       </c>
       <c r="D523" s="11" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
     </row>
     <row r="524" spans="2:4" x14ac:dyDescent="0.35">
@@ -8684,7 +8855,7 @@
         <v>527</v>
       </c>
       <c r="D524" s="11" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
     </row>
     <row r="525" spans="2:4" x14ac:dyDescent="0.35">
@@ -8695,7 +8866,7 @@
         <v>528</v>
       </c>
       <c r="D525" s="11" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="526" spans="2:4" x14ac:dyDescent="0.35">
@@ -8706,7 +8877,7 @@
         <v>529</v>
       </c>
       <c r="D526" s="11" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="527" spans="2:4" x14ac:dyDescent="0.35">
@@ -8717,7 +8888,7 @@
         <v>530</v>
       </c>
       <c r="D527" s="11" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="528" spans="2:4" x14ac:dyDescent="0.35">
@@ -8728,7 +8899,7 @@
         <v>531</v>
       </c>
       <c r="D528" s="11" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="529" spans="2:4" x14ac:dyDescent="0.35">
@@ -8739,7 +8910,7 @@
         <v>532</v>
       </c>
       <c r="D529" s="11" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
     </row>
     <row r="530" spans="2:4" x14ac:dyDescent="0.35">
@@ -8750,7 +8921,7 @@
         <v>533</v>
       </c>
       <c r="D530" s="11" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="531" spans="2:4" x14ac:dyDescent="0.35">
@@ -8761,7 +8932,7 @@
         <v>534</v>
       </c>
       <c r="D531" s="11" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="532" spans="2:4" x14ac:dyDescent="0.35">
@@ -8772,7 +8943,7 @@
         <v>535</v>
       </c>
       <c r="D532" s="11" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="533" spans="2:4" x14ac:dyDescent="0.35">
@@ -8783,7 +8954,7 @@
         <v>536</v>
       </c>
       <c r="D533" s="11" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="534" spans="2:4" x14ac:dyDescent="0.35">
@@ -8794,7 +8965,7 @@
         <v>537</v>
       </c>
       <c r="D534" s="11" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="535" spans="2:4" x14ac:dyDescent="0.35">
@@ -8805,7 +8976,7 @@
         <v>538</v>
       </c>
       <c r="D535" s="11" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
     </row>
     <row r="536" spans="2:4" x14ac:dyDescent="0.35">
@@ -8816,7 +8987,7 @@
         <v>539</v>
       </c>
       <c r="D536" s="11" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
     </row>
     <row r="537" spans="2:4" x14ac:dyDescent="0.35">
@@ -8827,7 +8998,7 @@
         <v>540</v>
       </c>
       <c r="D537" s="11" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
     </row>
     <row r="538" spans="2:4" x14ac:dyDescent="0.35">
@@ -8838,7 +9009,7 @@
         <v>541</v>
       </c>
       <c r="D538" s="11" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
     </row>
     <row r="539" spans="2:4" x14ac:dyDescent="0.35">
@@ -8849,7 +9020,7 @@
         <v>542</v>
       </c>
       <c r="D539" s="11" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
     </row>
     <row r="540" spans="2:4" x14ac:dyDescent="0.35">
@@ -8860,7 +9031,7 @@
         <v>543</v>
       </c>
       <c r="D540" s="11" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
     </row>
     <row r="541" spans="2:4" x14ac:dyDescent="0.35">
@@ -8871,7 +9042,7 @@
         <v>544</v>
       </c>
       <c r="D541" s="11" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
     </row>
     <row r="542" spans="2:4" x14ac:dyDescent="0.35">
@@ -8882,7 +9053,7 @@
         <v>545</v>
       </c>
       <c r="D542" s="11" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
     </row>
     <row r="543" spans="2:4" x14ac:dyDescent="0.35">
@@ -8893,7 +9064,7 @@
         <v>546</v>
       </c>
       <c r="D543" s="11" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
     </row>
     <row r="544" spans="2:4" x14ac:dyDescent="0.35">
@@ -8904,7 +9075,7 @@
         <v>547</v>
       </c>
       <c r="D544" s="11" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
     </row>
     <row r="545" spans="2:4" x14ac:dyDescent="0.35">
@@ -8915,7 +9086,7 @@
         <v>548</v>
       </c>
       <c r="D545" s="11" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="546" spans="2:4" x14ac:dyDescent="0.35">
@@ -8926,7 +9097,7 @@
         <v>549</v>
       </c>
       <c r="D546" s="11" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="547" spans="2:4" x14ac:dyDescent="0.35">
@@ -8937,7 +9108,7 @@
         <v>550</v>
       </c>
       <c r="D547" s="11" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="548" spans="2:4" x14ac:dyDescent="0.35">
@@ -8948,7 +9119,7 @@
         <v>551</v>
       </c>
       <c r="D548" s="11" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="549" spans="2:4" x14ac:dyDescent="0.35">
@@ -8959,7 +9130,7 @@
         <v>552</v>
       </c>
       <c r="D549" s="11" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
     </row>
     <row r="550" spans="2:4" x14ac:dyDescent="0.35">
@@ -8970,7 +9141,7 @@
         <v>553</v>
       </c>
       <c r="D550" s="11" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
     </row>
     <row r="551" spans="2:4" x14ac:dyDescent="0.35">
@@ -8981,7 +9152,7 @@
         <v>554</v>
       </c>
       <c r="D551" s="11" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
     </row>
     <row r="552" spans="2:4" x14ac:dyDescent="0.35">
@@ -8992,7 +9163,7 @@
         <v>555</v>
       </c>
       <c r="D552" s="11" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
     </row>
     <row r="553" spans="2:4" x14ac:dyDescent="0.35">
@@ -9003,7 +9174,7 @@
         <v>556</v>
       </c>
       <c r="D553" s="11" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
     </row>
     <row r="554" spans="2:4" x14ac:dyDescent="0.35">
@@ -9014,7 +9185,7 @@
         <v>557</v>
       </c>
       <c r="D554" s="11" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
     </row>
     <row r="555" spans="2:4" x14ac:dyDescent="0.35">
@@ -9025,7 +9196,7 @@
         <v>558</v>
       </c>
       <c r="D555" s="11" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
     </row>
     <row r="556" spans="2:4" x14ac:dyDescent="0.35">
@@ -9036,7 +9207,7 @@
         <v>559</v>
       </c>
       <c r="D556" s="11" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
     </row>
     <row r="557" spans="2:4" x14ac:dyDescent="0.35">
@@ -9047,7 +9218,7 @@
         <v>560</v>
       </c>
       <c r="D557" s="11" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
     </row>
     <row r="558" spans="2:4" x14ac:dyDescent="0.35">
@@ -9058,7 +9229,7 @@
         <v>561</v>
       </c>
       <c r="D558" s="11" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
     </row>
     <row r="559" spans="2:4" x14ac:dyDescent="0.35">
@@ -9069,7 +9240,7 @@
         <v>562</v>
       </c>
       <c r="D559" s="11" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
     </row>
     <row r="560" spans="2:4" x14ac:dyDescent="0.35">
@@ -9080,7 +9251,7 @@
         <v>563</v>
       </c>
       <c r="D560" s="11" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
     </row>
     <row r="561" spans="2:4" x14ac:dyDescent="0.35">
@@ -9091,7 +9262,7 @@
         <v>564</v>
       </c>
       <c r="D561" s="11" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
     </row>
     <row r="562" spans="2:4" x14ac:dyDescent="0.35">
@@ -9102,7 +9273,7 @@
         <v>565</v>
       </c>
       <c r="D562" s="11" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
     </row>
     <row r="563" spans="2:4" x14ac:dyDescent="0.35">
@@ -9113,7 +9284,7 @@
         <v>566</v>
       </c>
       <c r="D563" s="11" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
     </row>
     <row r="564" spans="2:4" x14ac:dyDescent="0.35">
@@ -9124,7 +9295,7 @@
         <v>567</v>
       </c>
       <c r="D564" s="11" t="s">
-        <v>769</v>
+        <v>792</v>
       </c>
     </row>
     <row r="565" spans="2:4" x14ac:dyDescent="0.35">
@@ -9135,7 +9306,7 @@
         <v>568</v>
       </c>
       <c r="D565" s="11" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
     </row>
     <row r="566" spans="2:4" x14ac:dyDescent="0.35">
@@ -9146,7 +9317,7 @@
         <v>569</v>
       </c>
       <c r="D566" s="11" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
     </row>
     <row r="567" spans="2:4" x14ac:dyDescent="0.35">
@@ -9157,7 +9328,7 @@
         <v>570</v>
       </c>
       <c r="D567" s="11" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
     </row>
     <row r="568" spans="2:4" x14ac:dyDescent="0.35">
@@ -9168,7 +9339,7 @@
         <v>571</v>
       </c>
       <c r="D568" s="11" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
     </row>
     <row r="569" spans="2:4" x14ac:dyDescent="0.35">
@@ -9179,7 +9350,7 @@
         <v>572</v>
       </c>
       <c r="D569" s="11" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
     </row>
     <row r="570" spans="2:4" x14ac:dyDescent="0.35">
@@ -9190,7 +9361,7 @@
         <v>573</v>
       </c>
       <c r="D570" s="11" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
     </row>
     <row r="571" spans="2:4" x14ac:dyDescent="0.35">
@@ -9201,7 +9372,7 @@
         <v>574</v>
       </c>
       <c r="D571" s="11" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
     </row>
     <row r="572" spans="2:4" x14ac:dyDescent="0.35">
@@ -9212,7 +9383,7 @@
         <v>575</v>
       </c>
       <c r="D572" s="11" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
     </row>
     <row r="573" spans="2:4" x14ac:dyDescent="0.35">
@@ -9223,7 +9394,7 @@
         <v>576</v>
       </c>
       <c r="D573" s="11" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
     </row>
     <row r="574" spans="2:4" x14ac:dyDescent="0.35">
@@ -9234,7 +9405,7 @@
         <v>577</v>
       </c>
       <c r="D574" s="11" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
     </row>
     <row r="575" spans="2:4" x14ac:dyDescent="0.35">
@@ -9245,7 +9416,7 @@
         <v>578</v>
       </c>
       <c r="D575" s="11" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
     </row>
     <row r="576" spans="2:4" x14ac:dyDescent="0.35">
@@ -9256,7 +9427,7 @@
         <v>579</v>
       </c>
       <c r="D576" s="11" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
     </row>
     <row r="577" spans="2:4" x14ac:dyDescent="0.35">
@@ -9267,7 +9438,7 @@
         <v>580</v>
       </c>
       <c r="D577" s="11" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
     </row>
     <row r="578" spans="2:4" x14ac:dyDescent="0.35">
@@ -9278,7 +9449,7 @@
         <v>581</v>
       </c>
       <c r="D578" s="11" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
     </row>
     <row r="579" spans="2:4" x14ac:dyDescent="0.35">
@@ -9289,7 +9460,7 @@
         <v>582</v>
       </c>
       <c r="D579" s="11" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
     </row>
     <row r="580" spans="2:4" x14ac:dyDescent="0.35">
@@ -9300,7 +9471,7 @@
         <v>583</v>
       </c>
       <c r="D580" s="11" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
     </row>
     <row r="581" spans="2:4" x14ac:dyDescent="0.35">
@@ -9311,7 +9482,7 @@
         <v>584</v>
       </c>
       <c r="D581" s="11" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
     </row>
     <row r="582" spans="2:4" x14ac:dyDescent="0.35">
@@ -9322,7 +9493,7 @@
         <v>585</v>
       </c>
       <c r="D582" s="11" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
     </row>
     <row r="583" spans="2:4" x14ac:dyDescent="0.35">
@@ -9333,7 +9504,7 @@
         <v>586</v>
       </c>
       <c r="D583" s="11" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
     </row>
     <row r="584" spans="2:4" x14ac:dyDescent="0.35">
@@ -9344,7 +9515,7 @@
         <v>587</v>
       </c>
       <c r="D584" s="11" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
     </row>
     <row r="585" spans="2:4" x14ac:dyDescent="0.35">
@@ -9355,7 +9526,7 @@
         <v>588</v>
       </c>
       <c r="D585" s="11" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="586" spans="2:4" x14ac:dyDescent="0.35">
@@ -9366,7 +9537,7 @@
         <v>589</v>
       </c>
       <c r="D586" s="11" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="587" spans="2:4" x14ac:dyDescent="0.35">
@@ -9377,7 +9548,7 @@
         <v>590</v>
       </c>
       <c r="D587" s="11" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="588" spans="2:4" x14ac:dyDescent="0.35">
@@ -9388,7 +9559,7 @@
         <v>591</v>
       </c>
       <c r="D588" s="11" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="589" spans="2:4" x14ac:dyDescent="0.35">
@@ -9399,7 +9570,7 @@
         <v>592</v>
       </c>
       <c r="D589" s="11" t="s">
-        <v>769</v>
+        <v>797</v>
       </c>
     </row>
     <row r="590" spans="2:4" x14ac:dyDescent="0.35">
@@ -9410,7 +9581,7 @@
         <v>593</v>
       </c>
       <c r="D590" s="11" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
     </row>
     <row r="591" spans="2:4" x14ac:dyDescent="0.35">
@@ -9421,7 +9592,7 @@
         <v>371</v>
       </c>
       <c r="D591" s="11" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
     </row>
     <row r="592" spans="2:4" x14ac:dyDescent="0.35">
@@ -9432,7 +9603,7 @@
         <v>594</v>
       </c>
       <c r="D592" s="11" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
     </row>
     <row r="593" spans="2:4" x14ac:dyDescent="0.35">
@@ -9443,7 +9614,7 @@
         <v>595</v>
       </c>
       <c r="D593" s="11" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
     </row>
     <row r="594" spans="2:4" x14ac:dyDescent="0.35">
@@ -9454,7 +9625,7 @@
         <v>596</v>
       </c>
       <c r="D594" s="11" t="s">
-        <v>769</v>
+        <v>798</v>
       </c>
     </row>
     <row r="595" spans="2:4" x14ac:dyDescent="0.35">
@@ -9465,7 +9636,7 @@
         <v>597</v>
       </c>
       <c r="D595" s="11" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
     </row>
     <row r="596" spans="2:4" x14ac:dyDescent="0.35">
@@ -9476,7 +9647,7 @@
         <v>598</v>
       </c>
       <c r="D596" s="11" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
     </row>
     <row r="597" spans="2:4" x14ac:dyDescent="0.35">
@@ -9487,7 +9658,7 @@
         <v>599</v>
       </c>
       <c r="D597" s="11" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
     </row>
     <row r="598" spans="2:4" x14ac:dyDescent="0.35">
@@ -9498,7 +9669,7 @@
         <v>600</v>
       </c>
       <c r="D598" s="11" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
     </row>
     <row r="599" spans="2:4" x14ac:dyDescent="0.35">
@@ -9509,7 +9680,7 @@
         <v>601</v>
       </c>
       <c r="D599" s="11" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
     </row>
     <row r="600" spans="2:4" x14ac:dyDescent="0.35">
@@ -9520,7 +9691,7 @@
         <v>602</v>
       </c>
       <c r="D600" s="11" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="601" spans="2:4" x14ac:dyDescent="0.35">
@@ -9531,7 +9702,7 @@
         <v>603</v>
       </c>
       <c r="D601" s="11" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="602" spans="2:4" x14ac:dyDescent="0.35">
@@ -9542,7 +9713,7 @@
         <v>604</v>
       </c>
       <c r="D602" s="11" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="603" spans="2:4" x14ac:dyDescent="0.35">
@@ -9553,7 +9724,7 @@
         <v>605</v>
       </c>
       <c r="D603" s="11" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="604" spans="2:4" x14ac:dyDescent="0.35">
@@ -9564,7 +9735,7 @@
         <v>606</v>
       </c>
       <c r="D604" s="11" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
     </row>
     <row r="605" spans="2:4" x14ac:dyDescent="0.35">
@@ -9575,7 +9746,7 @@
         <v>607</v>
       </c>
       <c r="D605" s="11" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
     </row>
     <row r="606" spans="2:4" x14ac:dyDescent="0.35">
@@ -9586,7 +9757,7 @@
         <v>608</v>
       </c>
       <c r="D606" s="11" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
     </row>
     <row r="607" spans="2:4" x14ac:dyDescent="0.35">
@@ -9597,7 +9768,7 @@
         <v>609</v>
       </c>
       <c r="D607" s="11" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
     </row>
     <row r="608" spans="2:4" x14ac:dyDescent="0.35">
@@ -9608,7 +9779,7 @@
         <v>610</v>
       </c>
       <c r="D608" s="11" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
     </row>
     <row r="609" spans="2:4" x14ac:dyDescent="0.35">
@@ -9619,7 +9790,7 @@
         <v>611</v>
       </c>
       <c r="D609" s="11" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
     </row>
     <row r="610" spans="2:4" x14ac:dyDescent="0.35">
@@ -9630,7 +9801,7 @@
         <v>612</v>
       </c>
       <c r="D610" s="11" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
     </row>
     <row r="611" spans="2:4" x14ac:dyDescent="0.35">
@@ -9641,7 +9812,7 @@
         <v>613</v>
       </c>
       <c r="D611" s="11" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
     </row>
     <row r="612" spans="2:4" x14ac:dyDescent="0.35">
@@ -9652,7 +9823,7 @@
         <v>614</v>
       </c>
       <c r="D612" s="11" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
     </row>
     <row r="613" spans="2:4" x14ac:dyDescent="0.35">
@@ -9663,7 +9834,7 @@
         <v>615</v>
       </c>
       <c r="D613" s="11" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
     </row>
     <row r="614" spans="2:4" x14ac:dyDescent="0.35">
@@ -9674,7 +9845,7 @@
         <v>328</v>
       </c>
       <c r="D614" s="11" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
     </row>
     <row r="615" spans="2:4" x14ac:dyDescent="0.35">
@@ -9685,7 +9856,7 @@
         <v>616</v>
       </c>
       <c r="D615" s="11" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
     </row>
     <row r="616" spans="2:4" x14ac:dyDescent="0.35">
@@ -9696,7 +9867,7 @@
         <v>617</v>
       </c>
       <c r="D616" s="11" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
     </row>
     <row r="617" spans="2:4" x14ac:dyDescent="0.35">
@@ -9707,7 +9878,7 @@
         <v>618</v>
       </c>
       <c r="D617" s="11" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
     </row>
     <row r="618" spans="2:4" x14ac:dyDescent="0.35">
@@ -9718,7 +9889,7 @@
         <v>619</v>
       </c>
       <c r="D618" s="11" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
     </row>
     <row r="619" spans="2:4" x14ac:dyDescent="0.35">
@@ -9729,7 +9900,7 @@
         <v>620</v>
       </c>
       <c r="D619" s="11" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
     </row>
     <row r="620" spans="2:4" x14ac:dyDescent="0.35">
@@ -9740,7 +9911,7 @@
         <v>621</v>
       </c>
       <c r="D620" s="11" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
     </row>
     <row r="621" spans="2:4" x14ac:dyDescent="0.35">
@@ -9751,7 +9922,7 @@
         <v>622</v>
       </c>
       <c r="D621" s="11" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
     </row>
     <row r="622" spans="2:4" x14ac:dyDescent="0.35">
@@ -9762,7 +9933,7 @@
         <v>623</v>
       </c>
       <c r="D622" s="11" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
     </row>
     <row r="623" spans="2:4" x14ac:dyDescent="0.35">
@@ -9773,7 +9944,7 @@
         <v>624</v>
       </c>
       <c r="D623" s="11" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
     </row>
     <row r="624" spans="2:4" x14ac:dyDescent="0.35">
@@ -9784,7 +9955,7 @@
         <v>625</v>
       </c>
       <c r="D624" s="11" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
     </row>
     <row r="625" spans="2:4" x14ac:dyDescent="0.35">
@@ -9795,7 +9966,7 @@
         <v>626</v>
       </c>
       <c r="D625" s="11" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
     </row>
     <row r="626" spans="2:4" x14ac:dyDescent="0.35">
@@ -9806,7 +9977,7 @@
         <v>627</v>
       </c>
       <c r="D626" s="11" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
     </row>
     <row r="627" spans="2:4" x14ac:dyDescent="0.35">
@@ -9817,7 +9988,7 @@
         <v>628</v>
       </c>
       <c r="D627" s="11" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
     </row>
     <row r="628" spans="2:4" x14ac:dyDescent="0.35">
@@ -9828,7 +9999,7 @@
         <v>629</v>
       </c>
       <c r="D628" s="11" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
     </row>
     <row r="629" spans="2:4" x14ac:dyDescent="0.35">
@@ -9839,7 +10010,7 @@
         <v>630</v>
       </c>
       <c r="D629" s="11" t="s">
-        <v>769</v>
+        <v>805</v>
       </c>
     </row>
     <row r="630" spans="2:4" x14ac:dyDescent="0.35">
@@ -9850,7 +10021,7 @@
         <v>631</v>
       </c>
       <c r="D630" s="11" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
     </row>
     <row r="631" spans="2:4" x14ac:dyDescent="0.35">
@@ -9861,7 +10032,7 @@
         <v>632</v>
       </c>
       <c r="D631" s="11" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
     </row>
     <row r="632" spans="2:4" x14ac:dyDescent="0.35">
@@ -9872,7 +10043,7 @@
         <v>633</v>
       </c>
       <c r="D632" s="11" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
     </row>
     <row r="633" spans="2:4" x14ac:dyDescent="0.35">
@@ -9883,7 +10054,7 @@
         <v>634</v>
       </c>
       <c r="D633" s="11" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
     </row>
     <row r="634" spans="2:4" x14ac:dyDescent="0.35">
@@ -9894,7 +10065,7 @@
         <v>635</v>
       </c>
       <c r="D634" s="11" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
     </row>
     <row r="635" spans="2:4" x14ac:dyDescent="0.35">
@@ -9905,7 +10076,7 @@
         <v>636</v>
       </c>
       <c r="D635" s="11" t="s">
-        <v>769</v>
+        <v>807</v>
       </c>
     </row>
     <row r="636" spans="2:4" x14ac:dyDescent="0.35">
@@ -9916,7 +10087,7 @@
         <v>637</v>
       </c>
       <c r="D636" s="11" t="s">
-        <v>769</v>
+        <v>807</v>
       </c>
     </row>
     <row r="637" spans="2:4" x14ac:dyDescent="0.35">
@@ -9927,7 +10098,7 @@
         <v>638</v>
       </c>
       <c r="D637" s="11" t="s">
-        <v>769</v>
+        <v>807</v>
       </c>
     </row>
     <row r="638" spans="2:4" x14ac:dyDescent="0.35">
@@ -9938,7 +10109,7 @@
         <v>639</v>
       </c>
       <c r="D638" s="11" t="s">
-        <v>769</v>
+        <v>807</v>
       </c>
     </row>
     <row r="639" spans="2:4" x14ac:dyDescent="0.35">
@@ -9949,7 +10120,7 @@
         <v>640</v>
       </c>
       <c r="D639" s="11" t="s">
-        <v>769</v>
+        <v>807</v>
       </c>
     </row>
     <row r="640" spans="2:4" x14ac:dyDescent="0.35">
@@ -9960,7 +10131,7 @@
         <v>641</v>
       </c>
       <c r="D640" s="11" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
     </row>
     <row r="641" spans="2:4" x14ac:dyDescent="0.35">
@@ -9971,7 +10142,7 @@
         <v>642</v>
       </c>
       <c r="D641" s="11" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
     </row>
     <row r="642" spans="2:4" x14ac:dyDescent="0.35">
@@ -9982,7 +10153,7 @@
         <v>643</v>
       </c>
       <c r="D642" s="11" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
     </row>
     <row r="643" spans="2:4" x14ac:dyDescent="0.35">
@@ -9993,7 +10164,7 @@
         <v>644</v>
       </c>
       <c r="D643" s="11" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
     </row>
     <row r="644" spans="2:4" x14ac:dyDescent="0.35">
@@ -10004,7 +10175,7 @@
         <v>645</v>
       </c>
       <c r="D644" s="11" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
     </row>
     <row r="645" spans="2:4" x14ac:dyDescent="0.35">
@@ -10015,7 +10186,7 @@
         <v>646</v>
       </c>
       <c r="D645" s="11" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
     </row>
     <row r="646" spans="2:4" x14ac:dyDescent="0.35">
@@ -10026,7 +10197,7 @@
         <v>647</v>
       </c>
       <c r="D646" s="11" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
     </row>
     <row r="647" spans="2:4" x14ac:dyDescent="0.35">
@@ -10037,7 +10208,7 @@
         <v>648</v>
       </c>
       <c r="D647" s="11" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
     </row>
     <row r="648" spans="2:4" x14ac:dyDescent="0.35">
@@ -10048,7 +10219,7 @@
         <v>649</v>
       </c>
       <c r="D648" s="11" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
     </row>
     <row r="649" spans="2:4" x14ac:dyDescent="0.35">
@@ -10059,7 +10230,7 @@
         <v>650</v>
       </c>
       <c r="D649" s="11" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
     </row>
     <row r="650" spans="2:4" x14ac:dyDescent="0.35">
@@ -10070,7 +10241,7 @@
         <v>651</v>
       </c>
       <c r="D650" s="11" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
     </row>
     <row r="651" spans="2:4" x14ac:dyDescent="0.35">
@@ -10081,7 +10252,7 @@
         <v>652</v>
       </c>
       <c r="D651" s="11" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
     </row>
     <row r="652" spans="2:4" x14ac:dyDescent="0.35">
@@ -10092,7 +10263,7 @@
         <v>103</v>
       </c>
       <c r="D652" s="11" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
     </row>
     <row r="653" spans="2:4" x14ac:dyDescent="0.35">
@@ -10103,7 +10274,7 @@
         <v>653</v>
       </c>
       <c r="D653" s="11" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
     </row>
     <row r="654" spans="2:4" x14ac:dyDescent="0.35">
@@ -10114,7 +10285,7 @@
         <v>654</v>
       </c>
       <c r="D654" s="11" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
     </row>
     <row r="655" spans="2:4" x14ac:dyDescent="0.35">
@@ -10125,7 +10296,7 @@
         <v>655</v>
       </c>
       <c r="D655" s="11" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="656" spans="2:4" x14ac:dyDescent="0.35">
@@ -10136,7 +10307,7 @@
         <v>656</v>
       </c>
       <c r="D656" s="11" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="657" spans="2:4" x14ac:dyDescent="0.35">
@@ -10147,7 +10318,7 @@
         <v>657</v>
       </c>
       <c r="D657" s="11" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="658" spans="2:4" x14ac:dyDescent="0.35">
@@ -10158,7 +10329,7 @@
         <v>658</v>
       </c>
       <c r="D658" s="11" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="659" spans="2:4" x14ac:dyDescent="0.35">
@@ -10169,7 +10340,7 @@
         <v>659</v>
       </c>
       <c r="D659" s="11" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="660" spans="2:4" x14ac:dyDescent="0.35">
@@ -10180,7 +10351,7 @@
         <v>660</v>
       </c>
       <c r="D660" s="11" t="s">
-        <v>769</v>
+        <v>812</v>
       </c>
     </row>
     <row r="661" spans="2:4" x14ac:dyDescent="0.35">
@@ -10191,7 +10362,7 @@
         <v>661</v>
       </c>
       <c r="D661" s="11" t="s">
-        <v>769</v>
+        <v>812</v>
       </c>
     </row>
     <row r="662" spans="2:4" x14ac:dyDescent="0.35">
@@ -10202,7 +10373,7 @@
         <v>662</v>
       </c>
       <c r="D662" s="11" t="s">
-        <v>769</v>
+        <v>812</v>
       </c>
     </row>
     <row r="663" spans="2:4" x14ac:dyDescent="0.35">
@@ -10213,7 +10384,7 @@
         <v>663</v>
       </c>
       <c r="D663" s="11" t="s">
-        <v>769</v>
+        <v>812</v>
       </c>
     </row>
     <row r="664" spans="2:4" x14ac:dyDescent="0.35">
@@ -10224,7 +10395,7 @@
         <v>664</v>
       </c>
       <c r="D664" s="11" t="s">
-        <v>769</v>
+        <v>812</v>
       </c>
     </row>
     <row r="665" spans="2:4" x14ac:dyDescent="0.35">
@@ -10235,7 +10406,7 @@
         <v>665</v>
       </c>
       <c r="D665" s="11" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
     </row>
     <row r="666" spans="2:4" x14ac:dyDescent="0.35">
@@ -10246,7 +10417,7 @@
         <v>666</v>
       </c>
       <c r="D666" s="11" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
     </row>
     <row r="667" spans="2:4" x14ac:dyDescent="0.35">
@@ -10257,7 +10428,7 @@
         <v>667</v>
       </c>
       <c r="D667" s="11" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
     </row>
     <row r="668" spans="2:4" x14ac:dyDescent="0.35">
@@ -10268,7 +10439,7 @@
         <v>668</v>
       </c>
       <c r="D668" s="11" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
     </row>
     <row r="669" spans="2:4" x14ac:dyDescent="0.35">
@@ -10279,7 +10450,7 @@
         <v>669</v>
       </c>
       <c r="D669" s="11" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
     </row>
     <row r="670" spans="2:4" x14ac:dyDescent="0.35">
@@ -10290,7 +10461,7 @@
         <v>670</v>
       </c>
       <c r="D670" s="11" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
     </row>
     <row r="671" spans="2:4" x14ac:dyDescent="0.35">
@@ -10301,7 +10472,7 @@
         <v>671</v>
       </c>
       <c r="D671" s="11" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
     </row>
     <row r="672" spans="2:4" x14ac:dyDescent="0.35">
@@ -10312,7 +10483,7 @@
         <v>672</v>
       </c>
       <c r="D672" s="11" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
     </row>
     <row r="673" spans="2:4" x14ac:dyDescent="0.35">
@@ -10323,7 +10494,7 @@
         <v>673</v>
       </c>
       <c r="D673" s="11" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
     </row>
     <row r="674" spans="2:4" x14ac:dyDescent="0.35">
@@ -10334,7 +10505,7 @@
         <v>674</v>
       </c>
       <c r="D674" s="11" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
     </row>
     <row r="675" spans="2:4" x14ac:dyDescent="0.35">
@@ -10345,7 +10516,7 @@
         <v>675</v>
       </c>
       <c r="D675" s="11" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
     </row>
     <row r="676" spans="2:4" x14ac:dyDescent="0.35">
@@ -10356,7 +10527,7 @@
         <v>676</v>
       </c>
       <c r="D676" s="11" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
     </row>
     <row r="677" spans="2:4" x14ac:dyDescent="0.35">
@@ -10367,7 +10538,7 @@
         <v>677</v>
       </c>
       <c r="D677" s="11" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
     </row>
     <row r="678" spans="2:4" x14ac:dyDescent="0.35">
@@ -10378,7 +10549,7 @@
         <v>678</v>
       </c>
       <c r="D678" s="11" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
     </row>
     <row r="679" spans="2:4" x14ac:dyDescent="0.35">
@@ -10389,7 +10560,7 @@
         <v>679</v>
       </c>
       <c r="D679" s="11" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
     </row>
     <row r="680" spans="2:4" x14ac:dyDescent="0.35">
@@ -10400,7 +10571,7 @@
         <v>680</v>
       </c>
       <c r="D680" s="11" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
     </row>
     <row r="681" spans="2:4" x14ac:dyDescent="0.35">
@@ -10411,7 +10582,7 @@
         <v>681</v>
       </c>
       <c r="D681" s="11" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
     </row>
     <row r="682" spans="2:4" x14ac:dyDescent="0.35">
@@ -10422,7 +10593,7 @@
         <v>682</v>
       </c>
       <c r="D682" s="11" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
     </row>
     <row r="683" spans="2:4" x14ac:dyDescent="0.35">
@@ -10433,7 +10604,7 @@
         <v>683</v>
       </c>
       <c r="D683" s="11" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
     </row>
     <row r="684" spans="2:4" x14ac:dyDescent="0.35">
@@ -10444,7 +10615,7 @@
         <v>684</v>
       </c>
       <c r="D684" s="11" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
     </row>
     <row r="685" spans="2:4" x14ac:dyDescent="0.35">
@@ -10455,7 +10626,7 @@
         <v>685</v>
       </c>
       <c r="D685" s="11" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
     </row>
     <row r="686" spans="2:4" x14ac:dyDescent="0.35">
@@ -10466,7 +10637,7 @@
         <v>686</v>
       </c>
       <c r="D686" s="11" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
     </row>
     <row r="687" spans="2:4" x14ac:dyDescent="0.35">
@@ -10477,7 +10648,7 @@
         <v>687</v>
       </c>
       <c r="D687" s="11" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
     </row>
     <row r="688" spans="2:4" x14ac:dyDescent="0.35">
@@ -10488,7 +10659,7 @@
         <v>688</v>
       </c>
       <c r="D688" s="11" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
     </row>
     <row r="689" spans="2:4" x14ac:dyDescent="0.35">
@@ -10499,7 +10670,7 @@
         <v>689</v>
       </c>
       <c r="D689" s="11" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
     </row>
     <row r="690" spans="2:4" x14ac:dyDescent="0.35">
@@ -10510,7 +10681,7 @@
         <v>690</v>
       </c>
       <c r="D690" s="11" t="s">
-        <v>769</v>
+        <v>818</v>
       </c>
     </row>
     <row r="691" spans="2:4" x14ac:dyDescent="0.35">
@@ -10521,7 +10692,7 @@
         <v>691</v>
       </c>
       <c r="D691" s="11" t="s">
-        <v>769</v>
+        <v>818</v>
       </c>
     </row>
     <row r="692" spans="2:4" x14ac:dyDescent="0.35">
@@ -10532,7 +10703,7 @@
         <v>692</v>
       </c>
       <c r="D692" s="11" t="s">
-        <v>769</v>
+        <v>818</v>
       </c>
     </row>
     <row r="693" spans="2:4" x14ac:dyDescent="0.35">
@@ -10543,7 +10714,7 @@
         <v>693</v>
       </c>
       <c r="D693" s="11" t="s">
-        <v>769</v>
+        <v>818</v>
       </c>
     </row>
     <row r="694" spans="2:4" x14ac:dyDescent="0.35">
@@ -10554,7 +10725,7 @@
         <v>694</v>
       </c>
       <c r="D694" s="11" t="s">
-        <v>769</v>
+        <v>818</v>
       </c>
     </row>
     <row r="695" spans="2:4" x14ac:dyDescent="0.35">
@@ -10565,7 +10736,7 @@
         <v>695</v>
       </c>
       <c r="D695" s="11" t="s">
-        <v>769</v>
+        <v>819</v>
       </c>
     </row>
     <row r="696" spans="2:4" x14ac:dyDescent="0.35">
@@ -10576,7 +10747,7 @@
         <v>696</v>
       </c>
       <c r="D696" s="11" t="s">
-        <v>769</v>
+        <v>819</v>
       </c>
     </row>
     <row r="697" spans="2:4" x14ac:dyDescent="0.35">
@@ -10587,7 +10758,7 @@
         <v>697</v>
       </c>
       <c r="D697" s="11" t="s">
-        <v>769</v>
+        <v>819</v>
       </c>
     </row>
     <row r="698" spans="2:4" x14ac:dyDescent="0.35">
@@ -10598,7 +10769,7 @@
         <v>698</v>
       </c>
       <c r="D698" s="11" t="s">
-        <v>769</v>
+        <v>819</v>
       </c>
     </row>
     <row r="699" spans="2:4" x14ac:dyDescent="0.35">
@@ -10609,7 +10780,7 @@
         <v>699</v>
       </c>
       <c r="D699" s="11" t="s">
-        <v>769</v>
+        <v>819</v>
       </c>
     </row>
     <row r="700" spans="2:4" x14ac:dyDescent="0.35">
@@ -10620,7 +10791,7 @@
         <v>700</v>
       </c>
       <c r="D700" s="11" t="s">
-        <v>769</v>
+        <v>820</v>
       </c>
     </row>
     <row r="701" spans="2:4" x14ac:dyDescent="0.35">
@@ -10631,7 +10802,7 @@
         <v>701</v>
       </c>
       <c r="D701" s="11" t="s">
-        <v>769</v>
+        <v>820</v>
       </c>
     </row>
     <row r="702" spans="2:4" x14ac:dyDescent="0.35">
@@ -10642,7 +10813,7 @@
         <v>702</v>
       </c>
       <c r="D702" s="11" t="s">
-        <v>769</v>
+        <v>820</v>
       </c>
     </row>
     <row r="703" spans="2:4" x14ac:dyDescent="0.35">
@@ -10653,7 +10824,7 @@
         <v>703</v>
       </c>
       <c r="D703" s="11" t="s">
-        <v>769</v>
+        <v>820</v>
       </c>
     </row>
     <row r="704" spans="2:4" x14ac:dyDescent="0.35">
@@ -10664,7 +10835,7 @@
         <v>704</v>
       </c>
       <c r="D704" s="11" t="s">
-        <v>769</v>
+        <v>820</v>
       </c>
     </row>
     <row r="705" spans="2:4" x14ac:dyDescent="0.35">
@@ -10675,7 +10846,7 @@
         <v>705</v>
       </c>
       <c r="D705" s="11" t="s">
-        <v>769</v>
+        <v>821</v>
       </c>
     </row>
     <row r="706" spans="2:4" x14ac:dyDescent="0.35">
@@ -10686,7 +10857,7 @@
         <v>706</v>
       </c>
       <c r="D706" s="11" t="s">
-        <v>769</v>
+        <v>821</v>
       </c>
     </row>
     <row r="707" spans="2:4" x14ac:dyDescent="0.35">
@@ -10697,7 +10868,7 @@
         <v>707</v>
       </c>
       <c r="D707" s="11" t="s">
-        <v>769</v>
+        <v>821</v>
       </c>
     </row>
     <row r="708" spans="2:4" x14ac:dyDescent="0.35">
@@ -10708,7 +10879,7 @@
         <v>708</v>
       </c>
       <c r="D708" s="11" t="s">
-        <v>769</v>
+        <v>821</v>
       </c>
     </row>
     <row r="709" spans="2:4" x14ac:dyDescent="0.35">
@@ -10719,7 +10890,7 @@
         <v>709</v>
       </c>
       <c r="D709" s="11" t="s">
-        <v>769</v>
+        <v>821</v>
       </c>
     </row>
     <row r="710" spans="2:4" x14ac:dyDescent="0.35">
@@ -10730,7 +10901,7 @@
         <v>710</v>
       </c>
       <c r="D710" s="11" t="s">
-        <v>769</v>
+        <v>822</v>
       </c>
     </row>
     <row r="711" spans="2:4" x14ac:dyDescent="0.35">
@@ -10741,7 +10912,7 @@
         <v>711</v>
       </c>
       <c r="D711" s="11" t="s">
-        <v>769</v>
+        <v>822</v>
       </c>
     </row>
     <row r="712" spans="2:4" x14ac:dyDescent="0.35">
@@ -10752,7 +10923,7 @@
         <v>712</v>
       </c>
       <c r="D712" s="11" t="s">
-        <v>769</v>
+        <v>822</v>
       </c>
     </row>
     <row r="713" spans="2:4" x14ac:dyDescent="0.35">
@@ -10763,7 +10934,7 @@
         <v>713</v>
       </c>
       <c r="D713" s="11" t="s">
-        <v>769</v>
+        <v>822</v>
       </c>
     </row>
     <row r="714" spans="2:4" x14ac:dyDescent="0.35">
@@ -10774,7 +10945,7 @@
         <v>714</v>
       </c>
       <c r="D714" s="11" t="s">
-        <v>769</v>
+        <v>822</v>
       </c>
     </row>
     <row r="715" spans="2:4" x14ac:dyDescent="0.35">
@@ -10785,7 +10956,7 @@
         <v>715</v>
       </c>
       <c r="D715" s="11" t="s">
-        <v>769</v>
+        <v>823</v>
       </c>
     </row>
     <row r="716" spans="2:4" x14ac:dyDescent="0.35">
@@ -10796,7 +10967,7 @@
         <v>716</v>
       </c>
       <c r="D716" s="11" t="s">
-        <v>769</v>
+        <v>823</v>
       </c>
     </row>
     <row r="717" spans="2:4" x14ac:dyDescent="0.35">
@@ -10807,7 +10978,7 @@
         <v>717</v>
       </c>
       <c r="D717" s="11" t="s">
-        <v>769</v>
+        <v>823</v>
       </c>
     </row>
     <row r="718" spans="2:4" x14ac:dyDescent="0.35">
@@ -10818,7 +10989,7 @@
         <v>718</v>
       </c>
       <c r="D718" s="11" t="s">
-        <v>769</v>
+        <v>823</v>
       </c>
     </row>
     <row r="719" spans="2:4" x14ac:dyDescent="0.35">
@@ -10829,7 +11000,7 @@
         <v>719</v>
       </c>
       <c r="D719" s="11" t="s">
-        <v>769</v>
+        <v>823</v>
       </c>
     </row>
     <row r="720" spans="2:4" x14ac:dyDescent="0.35">
@@ -10840,7 +11011,7 @@
         <v>720</v>
       </c>
       <c r="D720" s="11" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
     </row>
     <row r="721" spans="2:4" x14ac:dyDescent="0.35">
@@ -10851,7 +11022,7 @@
         <v>721</v>
       </c>
       <c r="D721" s="11" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
     </row>
     <row r="722" spans="2:4" x14ac:dyDescent="0.35">
@@ -10862,7 +11033,7 @@
         <v>722</v>
       </c>
       <c r="D722" s="11" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
     </row>
     <row r="723" spans="2:4" x14ac:dyDescent="0.35">
@@ -10873,7 +11044,7 @@
         <v>723</v>
       </c>
       <c r="D723" s="11" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
     </row>
     <row r="724" spans="2:4" x14ac:dyDescent="0.35">
@@ -10884,7 +11055,7 @@
         <v>724</v>
       </c>
       <c r="D724" s="11" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
     </row>
     <row r="725" spans="2:4" x14ac:dyDescent="0.35">
@@ -10895,7 +11066,7 @@
         <v>725</v>
       </c>
       <c r="D725" s="11" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
     </row>
     <row r="726" spans="2:4" x14ac:dyDescent="0.35">
@@ -10906,7 +11077,7 @@
         <v>726</v>
       </c>
       <c r="D726" s="11" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
     </row>
     <row r="727" spans="2:4" x14ac:dyDescent="0.35">
@@ -10917,7 +11088,7 @@
         <v>727</v>
       </c>
       <c r="D727" s="11" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
     </row>
     <row r="728" spans="2:4" x14ac:dyDescent="0.35">
@@ -10928,7 +11099,7 @@
         <v>728</v>
       </c>
       <c r="D728" s="11" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
     </row>
     <row r="729" spans="2:4" x14ac:dyDescent="0.35">
@@ -10939,7 +11110,7 @@
         <v>729</v>
       </c>
       <c r="D729" s="11" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
     </row>
     <row r="730" spans="2:4" x14ac:dyDescent="0.35">
@@ -10950,7 +11121,7 @@
         <v>730</v>
       </c>
       <c r="D730" s="11" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
     </row>
     <row r="731" spans="2:4" x14ac:dyDescent="0.35">
@@ -10961,7 +11132,7 @@
         <v>731</v>
       </c>
       <c r="D731" s="11" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
     </row>
     <row r="732" spans="2:4" x14ac:dyDescent="0.35">
@@ -10972,7 +11143,7 @@
         <v>732</v>
       </c>
       <c r="D732" s="11" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
     </row>
     <row r="733" spans="2:4" x14ac:dyDescent="0.35">
@@ -10983,7 +11154,7 @@
         <v>733</v>
       </c>
       <c r="D733" s="11" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
     </row>
     <row r="734" spans="2:4" x14ac:dyDescent="0.35">
@@ -10994,7 +11165,7 @@
         <v>734</v>
       </c>
       <c r="D734" s="11" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
     </row>
     <row r="735" spans="2:4" x14ac:dyDescent="0.35">
@@ -11005,7 +11176,7 @@
         <v>735</v>
       </c>
       <c r="D735" s="11" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
     </row>
     <row r="736" spans="2:4" x14ac:dyDescent="0.35">
@@ -11016,7 +11187,7 @@
         <v>736</v>
       </c>
       <c r="D736" s="11" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
     </row>
     <row r="737" spans="2:4" x14ac:dyDescent="0.35">
@@ -11027,7 +11198,7 @@
         <v>737</v>
       </c>
       <c r="D737" s="11" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
     </row>
     <row r="738" spans="2:4" x14ac:dyDescent="0.35">
@@ -11038,7 +11209,7 @@
         <v>738</v>
       </c>
       <c r="D738" s="11" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
     </row>
     <row r="739" spans="2:4" x14ac:dyDescent="0.35">
@@ -11049,7 +11220,7 @@
         <v>739</v>
       </c>
       <c r="D739" s="11" t="s">
-        <v>769</v>
+        <v>827</v>
       </c>
     </row>
     <row r="740" spans="2:4" x14ac:dyDescent="0.35">
@@ -11060,7 +11231,7 @@
         <v>740</v>
       </c>
       <c r="D740" s="11" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
     </row>
     <row r="741" spans="2:4" x14ac:dyDescent="0.35">
@@ -11071,7 +11242,7 @@
         <v>741</v>
       </c>
       <c r="D741" s="11" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
     </row>
     <row r="742" spans="2:4" x14ac:dyDescent="0.35">
@@ -11082,7 +11253,7 @@
         <v>742</v>
       </c>
       <c r="D742" s="11" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
     </row>
     <row r="743" spans="2:4" x14ac:dyDescent="0.35">
@@ -11093,7 +11264,7 @@
         <v>743</v>
       </c>
       <c r="D743" s="11" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
     </row>
     <row r="744" spans="2:4" x14ac:dyDescent="0.35">
@@ -11104,7 +11275,7 @@
         <v>744</v>
       </c>
       <c r="D744" s="11" t="s">
-        <v>769</v>
+        <v>828</v>
       </c>
     </row>
     <row r="745" spans="2:4" x14ac:dyDescent="0.35">
@@ -11115,7 +11286,7 @@
         <v>745</v>
       </c>
       <c r="D745" s="11" t="s">
-        <v>769</v>
+        <v>829</v>
       </c>
     </row>
     <row r="746" spans="2:4" x14ac:dyDescent="0.35">
@@ -11126,7 +11297,7 @@
         <v>746</v>
       </c>
       <c r="D746" s="11" t="s">
-        <v>769</v>
+        <v>829</v>
       </c>
     </row>
     <row r="747" spans="2:4" x14ac:dyDescent="0.35">
@@ -11137,7 +11308,7 @@
         <v>747</v>
       </c>
       <c r="D747" s="11" t="s">
-        <v>769</v>
+        <v>829</v>
       </c>
     </row>
     <row r="748" spans="2:4" x14ac:dyDescent="0.35">
@@ -11148,7 +11319,7 @@
         <v>748</v>
       </c>
       <c r="D748" s="11" t="s">
-        <v>769</v>
+        <v>829</v>
       </c>
     </row>
     <row r="749" spans="2:4" x14ac:dyDescent="0.35">
@@ -11159,7 +11330,7 @@
         <v>749</v>
       </c>
       <c r="D749" s="11" t="s">
-        <v>769</v>
+        <v>829</v>
       </c>
     </row>
     <row r="750" spans="2:4" x14ac:dyDescent="0.35">
@@ -11170,7 +11341,7 @@
         <v>750</v>
       </c>
       <c r="D750" s="11" t="s">
-        <v>769</v>
+        <v>830</v>
       </c>
     </row>
     <row r="751" spans="2:4" x14ac:dyDescent="0.35">
@@ -11181,7 +11352,7 @@
         <v>751</v>
       </c>
       <c r="D751" s="11" t="s">
-        <v>769</v>
+        <v>830</v>
       </c>
     </row>
     <row r="752" spans="2:4" x14ac:dyDescent="0.35">
@@ -11192,7 +11363,7 @@
         <v>752</v>
       </c>
       <c r="D752" s="11" t="s">
-        <v>769</v>
+        <v>830</v>
       </c>
     </row>
     <row r="753" spans="2:4" x14ac:dyDescent="0.35">
@@ -11203,7 +11374,7 @@
         <v>753</v>
       </c>
       <c r="D753" s="11" t="s">
-        <v>769</v>
+        <v>830</v>
       </c>
     </row>
     <row r="754" spans="2:4" x14ac:dyDescent="0.35">
@@ -11214,7 +11385,7 @@
         <v>754</v>
       </c>
       <c r="D754" s="11" t="s">
-        <v>769</v>
+        <v>830</v>
       </c>
     </row>
     <row r="755" spans="2:4" x14ac:dyDescent="0.35">
@@ -11225,7 +11396,7 @@
         <v>755</v>
       </c>
       <c r="D755" s="11" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="756" spans="2:4" x14ac:dyDescent="0.35">
@@ -11236,7 +11407,7 @@
         <v>756</v>
       </c>
       <c r="D756" s="11" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="757" spans="2:4" x14ac:dyDescent="0.35">
@@ -11247,7 +11418,7 @@
         <v>757</v>
       </c>
       <c r="D757" s="11" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="758" spans="2:4" x14ac:dyDescent="0.35">
@@ -11258,7 +11429,7 @@
         <v>758</v>
       </c>
       <c r="D758" s="11" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="759" spans="2:4" x14ac:dyDescent="0.35">
@@ -11269,7 +11440,7 @@
         <v>759</v>
       </c>
       <c r="D759" s="11" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="760" spans="2:4" x14ac:dyDescent="0.35">
@@ -11280,7 +11451,7 @@
         <v>760</v>
       </c>
       <c r="D760" s="11" t="s">
-        <v>769</v>
+        <v>832</v>
       </c>
     </row>
     <row r="761" spans="2:4" x14ac:dyDescent="0.35">
@@ -11291,7 +11462,7 @@
         <v>761</v>
       </c>
       <c r="D761" s="11" t="s">
-        <v>769</v>
+        <v>832</v>
       </c>
     </row>
     <row r="762" spans="2:4" x14ac:dyDescent="0.35">
@@ -11302,7 +11473,7 @@
         <v>762</v>
       </c>
       <c r="D762" s="11" t="s">
-        <v>769</v>
+        <v>832</v>
       </c>
     </row>
     <row r="763" spans="2:4" x14ac:dyDescent="0.35">
@@ -11313,7 +11484,7 @@
         <v>763</v>
       </c>
       <c r="D763" s="11" t="s">
-        <v>769</v>
+        <v>832</v>
       </c>
     </row>
     <row r="764" spans="2:4" x14ac:dyDescent="0.35">
@@ -11324,7 +11495,7 @@
         <v>764</v>
       </c>
       <c r="D764" s="11" t="s">
-        <v>769</v>
+        <v>832</v>
       </c>
     </row>
     <row r="765" spans="2:4" x14ac:dyDescent="0.35">
@@ -11335,7 +11506,7 @@
         <v>765</v>
       </c>
       <c r="D765" s="11" t="s">
-        <v>769</v>
+        <v>833</v>
       </c>
     </row>
     <row r="766" spans="2:4" x14ac:dyDescent="0.35">
@@ -11346,7 +11517,7 @@
         <v>766</v>
       </c>
       <c r="D766" s="11" t="s">
-        <v>769</v>
+        <v>833</v>
       </c>
     </row>
     <row r="767" spans="2:4" x14ac:dyDescent="0.35">
@@ -11357,7 +11528,7 @@
         <v>767</v>
       </c>
       <c r="D767" s="11" t="s">
-        <v>769</v>
+        <v>833</v>
       </c>
     </row>
     <row r="768" spans="2:4" x14ac:dyDescent="0.35">
@@ -11368,7 +11539,7 @@
         <v>361</v>
       </c>
       <c r="D768" s="11" t="s">
-        <v>769</v>
+        <v>833</v>
       </c>
     </row>
     <row r="769" spans="2:4" x14ac:dyDescent="0.35">
@@ -11379,7 +11550,7 @@
         <v>768</v>
       </c>
       <c r="D769" s="11" t="s">
-        <v>769</v>
+        <v>833</v>
       </c>
     </row>
     <row r="770" spans="2:4" x14ac:dyDescent="0.35">

--- a/public/data/participant.xlsx
+++ b/public/data/participant.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="1995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="1996">
   <si>
     <t>No.</t>
   </si>
@@ -6124,6 +6124,9 @@
   </si>
   <si>
     <t>Dwi Cahya Rani S</t>
+  </si>
+  <si>
+    <t>Relay - TUPAI ACADEMY TEAM 0</t>
   </si>
 </sst>
 </file>
@@ -6301,7 +6304,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6344,6 +6347,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6665,7 +6671,7 @@
   <cols>
     <col min="2" max="2" width="7.6328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="45.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.54296875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14068,7 +14074,7 @@
         <v>453</v>
       </c>
       <c r="D673" s="6" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="674" spans="2:4" x14ac:dyDescent="0.35">
@@ -14123,7 +14129,7 @@
         <v>458</v>
       </c>
       <c r="D678" s="6" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="679" spans="2:4" x14ac:dyDescent="0.35">
@@ -14178,7 +14184,7 @@
         <v>463</v>
       </c>
       <c r="D683" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="684" spans="2:4" x14ac:dyDescent="0.35">
@@ -14233,7 +14239,7 @@
         <v>468</v>
       </c>
       <c r="D688" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="689" spans="2:4" x14ac:dyDescent="0.35">
@@ -14288,7 +14294,7 @@
         <v>473</v>
       </c>
       <c r="D693" s="6" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="694" spans="2:4" x14ac:dyDescent="0.35">
@@ -14343,7 +14349,7 @@
         <v>478</v>
       </c>
       <c r="D698" s="6" t="s">
-        <v>774</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="699" spans="2:4" x14ac:dyDescent="0.35">
@@ -14398,7 +14404,7 @@
         <v>483</v>
       </c>
       <c r="D703" s="6" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="704" spans="2:4" x14ac:dyDescent="0.35">
@@ -14453,7 +14459,7 @@
         <v>488</v>
       </c>
       <c r="D708" s="6" t="s">
-        <v>1057</v>
+        <v>775</v>
       </c>
     </row>
     <row r="709" spans="2:4" x14ac:dyDescent="0.35">
@@ -14508,7 +14514,7 @@
         <v>493</v>
       </c>
       <c r="D713" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="714" spans="2:4" x14ac:dyDescent="0.35">
@@ -14563,7 +14569,7 @@
         <v>498</v>
       </c>
       <c r="D718" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="719" spans="2:4" x14ac:dyDescent="0.35">
@@ -14618,7 +14624,7 @@
         <v>503</v>
       </c>
       <c r="D723" s="6" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="724" spans="2:4" x14ac:dyDescent="0.35">
@@ -14673,7 +14679,7 @@
         <v>508</v>
       </c>
       <c r="D728" s="6" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="729" spans="2:4" x14ac:dyDescent="0.35">
@@ -14728,7 +14734,7 @@
         <v>513</v>
       </c>
       <c r="D733" s="6" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="734" spans="2:4" x14ac:dyDescent="0.35">
@@ -14783,7 +14789,7 @@
         <v>518</v>
       </c>
       <c r="D738" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="739" spans="2:4" x14ac:dyDescent="0.35">
@@ -14838,7 +14844,7 @@
         <v>523</v>
       </c>
       <c r="D743" s="6" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="744" spans="2:4" x14ac:dyDescent="0.35">
@@ -14893,7 +14899,7 @@
         <v>528</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="749" spans="2:4" x14ac:dyDescent="0.35">
@@ -14948,7 +14954,7 @@
         <v>533</v>
       </c>
       <c r="D753" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="754" spans="2:4" x14ac:dyDescent="0.35">
@@ -15003,7 +15009,7 @@
         <v>538</v>
       </c>
       <c r="D758" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="759" spans="2:4" x14ac:dyDescent="0.35">
@@ -15058,7 +15064,7 @@
         <v>543</v>
       </c>
       <c r="D763" s="6" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="764" spans="2:4" x14ac:dyDescent="0.35">
@@ -15113,7 +15119,7 @@
         <v>548</v>
       </c>
       <c r="D768" s="6" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="769" spans="2:4" x14ac:dyDescent="0.35">
@@ -15168,7 +15174,7 @@
         <v>553</v>
       </c>
       <c r="D773" s="8" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="774" spans="2:4" x14ac:dyDescent="0.35">
@@ -15223,7 +15229,7 @@
         <v>558</v>
       </c>
       <c r="D778" s="8" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="779" spans="2:4" x14ac:dyDescent="0.35">
@@ -15278,7 +15284,7 @@
         <v>563</v>
       </c>
       <c r="D783" s="8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="784" spans="2:4" x14ac:dyDescent="0.35">
@@ -15333,7 +15339,7 @@
         <v>568</v>
       </c>
       <c r="D788" s="8" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="789" spans="2:4" x14ac:dyDescent="0.35">
@@ -15388,7 +15394,7 @@
         <v>573</v>
       </c>
       <c r="D793" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="794" spans="2:4" x14ac:dyDescent="0.35">
@@ -15443,7 +15449,7 @@
         <v>578</v>
       </c>
       <c r="D798" s="8" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="799" spans="2:4" x14ac:dyDescent="0.35">
@@ -15498,7 +15504,7 @@
         <v>583</v>
       </c>
       <c r="D803" s="8" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="804" spans="2:4" x14ac:dyDescent="0.35">
@@ -15553,7 +15559,7 @@
         <v>588</v>
       </c>
       <c r="D808" s="8" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="809" spans="2:4" x14ac:dyDescent="0.35">
@@ -15608,7 +15614,7 @@
         <v>593</v>
       </c>
       <c r="D813" s="8" t="s">
-        <v>795</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="814" spans="2:4" x14ac:dyDescent="0.35">
@@ -15663,7 +15669,7 @@
         <v>597</v>
       </c>
       <c r="D818" s="8" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="819" spans="2:4" x14ac:dyDescent="0.35">
@@ -15718,7 +15724,7 @@
         <v>602</v>
       </c>
       <c r="D823" s="8" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="824" spans="2:4" x14ac:dyDescent="0.35">
@@ -15773,7 +15779,7 @@
         <v>607</v>
       </c>
       <c r="D828" s="8" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="829" spans="2:4" x14ac:dyDescent="0.35">
@@ -15828,7 +15834,7 @@
         <v>612</v>
       </c>
       <c r="D833" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="834" spans="2:4" x14ac:dyDescent="0.35">
@@ -15883,7 +15889,7 @@
         <v>616</v>
       </c>
       <c r="D838" s="8" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="839" spans="2:4" x14ac:dyDescent="0.35">
@@ -15938,7 +15944,7 @@
         <v>621</v>
       </c>
       <c r="D843" s="8" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="844" spans="2:4" x14ac:dyDescent="0.35">
@@ -15993,7 +15999,7 @@
         <v>626</v>
       </c>
       <c r="D848" s="8" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="849" spans="2:4" x14ac:dyDescent="0.35">
@@ -16048,7 +16054,7 @@
         <v>631</v>
       </c>
       <c r="D853" s="8" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="854" spans="2:4" x14ac:dyDescent="0.35">
@@ -16103,7 +16109,7 @@
         <v>636</v>
       </c>
       <c r="D858" s="8" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="859" spans="2:4" x14ac:dyDescent="0.35">
@@ -16158,7 +16164,7 @@
         <v>641</v>
       </c>
       <c r="D863" s="8" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="864" spans="2:4" x14ac:dyDescent="0.35">
@@ -16213,7 +16219,7 @@
         <v>646</v>
       </c>
       <c r="D868" s="8" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="869" spans="2:4" x14ac:dyDescent="0.35">
@@ -16268,7 +16274,7 @@
         <v>651</v>
       </c>
       <c r="D873" s="8" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="874" spans="2:4" x14ac:dyDescent="0.35">
@@ -16323,7 +16329,7 @@
         <v>655</v>
       </c>
       <c r="D878" s="8" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="879" spans="2:4" x14ac:dyDescent="0.35">
@@ -16378,7 +16384,7 @@
         <v>660</v>
       </c>
       <c r="D883" s="6" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="884" spans="2:4" x14ac:dyDescent="0.35">
@@ -16433,7 +16439,7 @@
         <v>665</v>
       </c>
       <c r="D888" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="889" spans="2:4" x14ac:dyDescent="0.35">
@@ -16488,7 +16494,7 @@
         <v>670</v>
       </c>
       <c r="D893" s="6" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="894" spans="2:4" x14ac:dyDescent="0.35">
@@ -16543,7 +16549,7 @@
         <v>675</v>
       </c>
       <c r="D898" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="899" spans="2:4" x14ac:dyDescent="0.35">
@@ -16598,7 +16604,7 @@
         <v>680</v>
       </c>
       <c r="D903" s="6" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="904" spans="2:4" x14ac:dyDescent="0.35">
@@ -16653,7 +16659,7 @@
         <v>685</v>
       </c>
       <c r="D908" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="909" spans="2:4" x14ac:dyDescent="0.35">
@@ -16708,7 +16714,7 @@
         <v>690</v>
       </c>
       <c r="D913" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="914" spans="2:4" x14ac:dyDescent="0.35">
@@ -16763,7 +16769,7 @@
         <v>695</v>
       </c>
       <c r="D918" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="919" spans="2:4" x14ac:dyDescent="0.35">
@@ -16818,7 +16824,7 @@
         <v>700</v>
       </c>
       <c r="D923" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="924" spans="2:4" x14ac:dyDescent="0.35">
@@ -16873,7 +16879,7 @@
         <v>705</v>
       </c>
       <c r="D928" s="6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="929" spans="2:4" x14ac:dyDescent="0.35">
@@ -16928,7 +16934,7 @@
         <v>710</v>
       </c>
       <c r="D933" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="934" spans="2:4" x14ac:dyDescent="0.35">
@@ -16983,7 +16989,7 @@
         <v>715</v>
       </c>
       <c r="D938" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="939" spans="2:4" x14ac:dyDescent="0.35">
@@ -17038,7 +17044,7 @@
         <v>720</v>
       </c>
       <c r="D943" s="6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="944" spans="2:4" x14ac:dyDescent="0.35">
@@ -17093,7 +17099,7 @@
         <v>725</v>
       </c>
       <c r="D948" s="6" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="949" spans="2:4" x14ac:dyDescent="0.35">
@@ -17148,7 +17154,7 @@
         <v>730</v>
       </c>
       <c r="D953" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="954" spans="2:4" x14ac:dyDescent="0.35">
@@ -17203,7 +17209,7 @@
         <v>735</v>
       </c>
       <c r="D958" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="959" spans="2:4" x14ac:dyDescent="0.35">
@@ -17258,7 +17264,7 @@
         <v>740</v>
       </c>
       <c r="D963" s="6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="964" spans="2:4" x14ac:dyDescent="0.35">
@@ -17313,7 +17319,7 @@
         <v>745</v>
       </c>
       <c r="D968" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="969" spans="2:4" x14ac:dyDescent="0.35">
@@ -17368,7 +17374,7 @@
         <v>750</v>
       </c>
       <c r="D973" s="6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="974" spans="2:4" x14ac:dyDescent="0.35">
@@ -17423,7 +17429,7 @@
         <v>755</v>
       </c>
       <c r="D978" s="6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="979" spans="2:4" x14ac:dyDescent="0.35">
@@ -17478,7 +17484,7 @@
         <v>760</v>
       </c>
       <c r="D983" s="6" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="984" spans="2:4" x14ac:dyDescent="0.35">
@@ -17533,7 +17539,7 @@
         <v>765</v>
       </c>
       <c r="D988" s="6" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="989" spans="2:4" x14ac:dyDescent="0.35">
@@ -17588,7 +17594,7 @@
         <v>1163</v>
       </c>
       <c r="D993" s="6" t="s">
-        <v>831</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="994" spans="2:4" x14ac:dyDescent="0.35">
@@ -17643,7 +17649,7 @@
         <v>1168</v>
       </c>
       <c r="D998" s="6" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="999" spans="2:4" x14ac:dyDescent="0.35">
@@ -17698,7 +17704,7 @@
         <v>1173</v>
       </c>
       <c r="D1003" s="6" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1004" spans="2:4" x14ac:dyDescent="0.35">
@@ -17753,7 +17759,7 @@
         <v>1178</v>
       </c>
       <c r="D1008" s="6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="1009" spans="2:4" x14ac:dyDescent="0.35">
@@ -17808,7 +17814,7 @@
         <v>1183</v>
       </c>
       <c r="D1013" s="6" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="1014" spans="2:4" x14ac:dyDescent="0.35">
@@ -17863,7 +17869,7 @@
         <v>1188</v>
       </c>
       <c r="D1018" s="6" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="1019" spans="2:4" x14ac:dyDescent="0.35">
@@ -17918,7 +17924,7 @@
         <v>1193</v>
       </c>
       <c r="D1023" s="6" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="1024" spans="2:4" x14ac:dyDescent="0.35">
@@ -17973,7 +17979,7 @@
         <v>1198</v>
       </c>
       <c r="D1028" s="6" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="1029" spans="2:4" x14ac:dyDescent="0.35">
@@ -18028,7 +18034,7 @@
         <v>1203</v>
       </c>
       <c r="D1033" s="6" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="1034" spans="2:4" x14ac:dyDescent="0.35">
@@ -18083,7 +18089,7 @@
         <v>1208</v>
       </c>
       <c r="D1038" s="6" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="1039" spans="2:4" x14ac:dyDescent="0.35">
@@ -18138,7 +18144,7 @@
         <v>1213</v>
       </c>
       <c r="D1043" s="6" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="1044" spans="2:4" x14ac:dyDescent="0.35">
@@ -18193,7 +18199,7 @@
         <v>1218</v>
       </c>
       <c r="D1048" s="6" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="1049" spans="2:4" x14ac:dyDescent="0.35">
@@ -18248,7 +18254,7 @@
         <v>1223</v>
       </c>
       <c r="D1053" s="6" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="1054" spans="2:4" x14ac:dyDescent="0.35">
@@ -18303,7 +18309,7 @@
         <v>1228</v>
       </c>
       <c r="D1058" s="6" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="1059" spans="2:4" x14ac:dyDescent="0.35">
@@ -18358,7 +18364,7 @@
         <v>1233</v>
       </c>
       <c r="D1063" s="6" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="1064" spans="2:4" x14ac:dyDescent="0.35">
@@ -18413,7 +18419,7 @@
         <v>1238</v>
       </c>
       <c r="D1068" s="6" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="1069" spans="2:4" x14ac:dyDescent="0.35">
@@ -18468,7 +18474,7 @@
         <v>1243</v>
       </c>
       <c r="D1073" s="6" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="1074" spans="2:4" x14ac:dyDescent="0.35">
@@ -18523,7 +18529,7 @@
         <v>1248</v>
       </c>
       <c r="D1078" s="6" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="1079" spans="2:4" x14ac:dyDescent="0.35">
@@ -18578,7 +18584,7 @@
         <v>1253</v>
       </c>
       <c r="D1083" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="1084" spans="2:4" x14ac:dyDescent="0.35">
@@ -18633,7 +18639,7 @@
         <v>1258</v>
       </c>
       <c r="D1088" s="6" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="1089" spans="2:4" x14ac:dyDescent="0.35">
@@ -18688,7 +18694,7 @@
         <v>1263</v>
       </c>
       <c r="D1093" s="6" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="1094" spans="2:4" x14ac:dyDescent="0.35">
@@ -18743,7 +18749,7 @@
         <v>1268</v>
       </c>
       <c r="D1098" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="1099" spans="2:4" x14ac:dyDescent="0.35">
@@ -18798,7 +18804,7 @@
         <v>1273</v>
       </c>
       <c r="D1103" s="6" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1104" spans="2:4" x14ac:dyDescent="0.35">
@@ -18853,7 +18859,7 @@
         <v>1278</v>
       </c>
       <c r="D1108" s="6" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="1109" spans="2:4" x14ac:dyDescent="0.35">
@@ -18908,7 +18914,7 @@
         <v>1283</v>
       </c>
       <c r="D1113" s="6" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="1114" spans="2:4" x14ac:dyDescent="0.35">
@@ -18963,7 +18969,7 @@
         <v>1288</v>
       </c>
       <c r="D1118" s="6" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="1119" spans="2:4" x14ac:dyDescent="0.35">
@@ -19010,15 +19016,15 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="1123" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="1123" spans="2:4" ht="29" x14ac:dyDescent="0.35">
       <c r="B1123" s="5">
         <v>1122</v>
       </c>
       <c r="C1123" s="13" t="s">
         <v>1293</v>
       </c>
-      <c r="D1123" s="6" t="s">
-        <v>1083</v>
+      <c r="D1123" s="15" t="s">
+        <v>1084</v>
       </c>
     </row>
     <row r="1124" spans="2:4" x14ac:dyDescent="0.35">
@@ -19073,7 +19079,7 @@
         <v>1298</v>
       </c>
       <c r="D1128" s="6" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="1129" spans="2:4" x14ac:dyDescent="0.35">
@@ -19128,7 +19134,7 @@
         <v>1303</v>
       </c>
       <c r="D1133" s="6" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1134" spans="2:4" x14ac:dyDescent="0.35">
@@ -19183,7 +19189,7 @@
         <v>1308</v>
       </c>
       <c r="D1138" s="6" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="1139" spans="2:4" x14ac:dyDescent="0.35">
@@ -19238,7 +19244,7 @@
         <v>1313</v>
       </c>
       <c r="D1143" s="6" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1144" spans="2:4" x14ac:dyDescent="0.35">
@@ -19293,7 +19299,7 @@
         <v>1318</v>
       </c>
       <c r="D1148" s="6" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="1149" spans="2:4" x14ac:dyDescent="0.35">
@@ -19348,7 +19354,7 @@
         <v>1323</v>
       </c>
       <c r="D1153" s="6" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1154" spans="2:4" x14ac:dyDescent="0.35">
@@ -19403,7 +19409,7 @@
         <v>1327</v>
       </c>
       <c r="D1158" s="6" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="1159" spans="2:4" x14ac:dyDescent="0.35">
@@ -19458,7 +19464,7 @@
         <v>1332</v>
       </c>
       <c r="D1163" s="6" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="1164" spans="2:4" x14ac:dyDescent="0.35">
@@ -19513,7 +19519,7 @@
         <v>1337</v>
       </c>
       <c r="D1168" s="6" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="1169" spans="2:4" x14ac:dyDescent="0.35">
@@ -19568,7 +19574,7 @@
         <v>1342</v>
       </c>
       <c r="D1173" s="6" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1174" spans="2:4" x14ac:dyDescent="0.35">
@@ -19623,7 +19629,7 @@
         <v>1347</v>
       </c>
       <c r="D1178" s="6" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="1179" spans="2:4" x14ac:dyDescent="0.35">
@@ -19678,7 +19684,7 @@
         <v>1352</v>
       </c>
       <c r="D1183" s="6" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1184" spans="2:4" x14ac:dyDescent="0.35">
@@ -19733,7 +19739,7 @@
         <v>1357</v>
       </c>
       <c r="D1188" s="6" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1189" spans="2:4" x14ac:dyDescent="0.35">
@@ -19788,7 +19794,7 @@
         <v>1362</v>
       </c>
       <c r="D1193" s="6" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1194" spans="2:4" x14ac:dyDescent="0.35">
@@ -19843,7 +19849,7 @@
         <v>1367</v>
       </c>
       <c r="D1198" s="6" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="1199" spans="2:4" x14ac:dyDescent="0.35">
@@ -19898,7 +19904,7 @@
         <v>1372</v>
       </c>
       <c r="D1203" s="6" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1204" spans="2:4" x14ac:dyDescent="0.35">
@@ -19953,7 +19959,7 @@
         <v>1377</v>
       </c>
       <c r="D1208" s="6" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="1209" spans="2:4" x14ac:dyDescent="0.35">
@@ -20008,7 +20014,7 @@
         <v>1382</v>
       </c>
       <c r="D1213" s="6" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="1214" spans="2:4" x14ac:dyDescent="0.35">
@@ -20063,7 +20069,7 @@
         <v>1387</v>
       </c>
       <c r="D1218" s="6" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="1219" spans="2:4" x14ac:dyDescent="0.35">
@@ -20118,7 +20124,7 @@
         <v>1392</v>
       </c>
       <c r="D1223" s="6" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="1224" spans="2:4" x14ac:dyDescent="0.35">
@@ -20173,7 +20179,7 @@
         <v>1397</v>
       </c>
       <c r="D1228" s="6" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="1229" spans="2:4" x14ac:dyDescent="0.35">
@@ -20228,7 +20234,7 @@
         <v>1402</v>
       </c>
       <c r="D1233" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="1234" spans="2:4" x14ac:dyDescent="0.35">
@@ -20283,7 +20289,7 @@
         <v>1407</v>
       </c>
       <c r="D1238" s="6" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="1239" spans="2:4" x14ac:dyDescent="0.35">
@@ -20338,7 +20344,7 @@
         <v>1412</v>
       </c>
       <c r="D1243" s="6" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="1244" spans="2:4" x14ac:dyDescent="0.35">
@@ -20393,7 +20399,7 @@
         <v>1417</v>
       </c>
       <c r="D1248" s="6" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1249" spans="2:4" x14ac:dyDescent="0.35">
@@ -20448,7 +20454,7 @@
         <v>1422</v>
       </c>
       <c r="D1253" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="1254" spans="2:4" x14ac:dyDescent="0.35">
@@ -20503,7 +20509,7 @@
         <v>1427</v>
       </c>
       <c r="D1258" s="6" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="1259" spans="2:4" x14ac:dyDescent="0.35">
@@ -20558,7 +20564,7 @@
         <v>1432</v>
       </c>
       <c r="D1263" s="6" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="1264" spans="2:4" x14ac:dyDescent="0.35">
@@ -20613,7 +20619,7 @@
         <v>1437</v>
       </c>
       <c r="D1268" s="6" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="1269" spans="2:4" x14ac:dyDescent="0.35">
@@ -20668,7 +20674,7 @@
         <v>1442</v>
       </c>
       <c r="D1273" s="6" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1274" spans="2:4" x14ac:dyDescent="0.35">
@@ -20723,7 +20729,7 @@
         <v>1447</v>
       </c>
       <c r="D1278" s="6" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="1279" spans="2:4" x14ac:dyDescent="0.35">
@@ -20778,7 +20784,7 @@
         <v>1452</v>
       </c>
       <c r="D1283" s="6" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1284" spans="2:4" x14ac:dyDescent="0.35">
@@ -20833,7 +20839,7 @@
         <v>1457</v>
       </c>
       <c r="D1288" s="6" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1289" spans="2:4" x14ac:dyDescent="0.35">
@@ -20888,7 +20894,7 @@
         <v>1462</v>
       </c>
       <c r="D1293" s="6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="1294" spans="2:4" x14ac:dyDescent="0.35">
@@ -20943,7 +20949,7 @@
         <v>1467</v>
       </c>
       <c r="D1298" s="6" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="1299" spans="2:4" x14ac:dyDescent="0.35">
@@ -20998,7 +21004,7 @@
         <v>1472</v>
       </c>
       <c r="D1303" s="6" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="1304" spans="2:4" x14ac:dyDescent="0.35">
@@ -21053,7 +21059,7 @@
         <v>1477</v>
       </c>
       <c r="D1308" s="6" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1309" spans="2:4" x14ac:dyDescent="0.35">
@@ -21108,7 +21114,7 @@
         <v>1482</v>
       </c>
       <c r="D1313" s="6" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1314" spans="2:4" x14ac:dyDescent="0.35">
@@ -21163,7 +21169,7 @@
         <v>1487</v>
       </c>
       <c r="D1318" s="6" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1319" spans="2:4" x14ac:dyDescent="0.35">
@@ -21218,7 +21224,7 @@
         <v>1492</v>
       </c>
       <c r="D1323" s="6" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="1324" spans="2:4" x14ac:dyDescent="0.35">
@@ -21273,7 +21279,7 @@
         <v>1497</v>
       </c>
       <c r="D1328" s="6" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1329" spans="2:4" x14ac:dyDescent="0.35">
@@ -21328,7 +21334,7 @@
         <v>1502</v>
       </c>
       <c r="D1333" s="6" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="1334" spans="2:4" x14ac:dyDescent="0.35">
@@ -21383,7 +21389,7 @@
         <v>1507</v>
       </c>
       <c r="D1338" s="6" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1339" spans="2:4" x14ac:dyDescent="0.35">
@@ -21438,7 +21444,7 @@
         <v>1512</v>
       </c>
       <c r="D1343" s="6" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1344" spans="2:4" x14ac:dyDescent="0.35">
@@ -21493,7 +21499,7 @@
         <v>1517</v>
       </c>
       <c r="D1348" s="6" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1349" spans="2:4" x14ac:dyDescent="0.35">
@@ -21548,7 +21554,7 @@
         <v>1522</v>
       </c>
       <c r="D1353" s="6" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1354" spans="2:4" x14ac:dyDescent="0.35">
@@ -21603,7 +21609,7 @@
         <v>1324</v>
       </c>
       <c r="D1358" s="6" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1359" spans="2:4" x14ac:dyDescent="0.35">
@@ -21658,7 +21664,7 @@
         <v>1531</v>
       </c>
       <c r="D1363" s="6" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="1364" spans="2:4" x14ac:dyDescent="0.35">
@@ -21713,7 +21719,7 @@
         <v>1536</v>
       </c>
       <c r="D1368" s="6" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1369" spans="2:4" x14ac:dyDescent="0.35">
@@ -21768,7 +21774,7 @@
         <v>1541</v>
       </c>
       <c r="D1373" s="6" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1374" spans="2:4" x14ac:dyDescent="0.35">
@@ -21823,7 +21829,7 @@
         <v>1546</v>
       </c>
       <c r="D1378" s="6" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1379" spans="2:4" x14ac:dyDescent="0.35">
@@ -21878,7 +21884,7 @@
         <v>1472</v>
       </c>
       <c r="D1383" s="6" t="s">
-        <v>1135</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="1384" spans="2:4" x14ac:dyDescent="0.35">
@@ -21933,7 +21939,7 @@
         <v>1551</v>
       </c>
       <c r="D1388" s="6" t="s">
-        <v>1120</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1389" spans="2:4" x14ac:dyDescent="0.35">
@@ -21988,7 +21994,7 @@
         <v>1556</v>
       </c>
       <c r="D1393" s="6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1394" spans="2:4" x14ac:dyDescent="0.35">
@@ -22043,7 +22049,7 @@
         <v>1561</v>
       </c>
       <c r="D1398" s="6" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1399" spans="2:4" x14ac:dyDescent="0.35">
@@ -22098,7 +22104,7 @@
         <v>1566</v>
       </c>
       <c r="D1403" s="6" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1404" spans="2:4" x14ac:dyDescent="0.35">
@@ -22153,7 +22159,7 @@
         <v>1571</v>
       </c>
       <c r="D1408" s="6" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1409" spans="2:4" x14ac:dyDescent="0.35">
@@ -22208,7 +22214,7 @@
         <v>1576</v>
       </c>
       <c r="D1413" s="6" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1414" spans="2:4" x14ac:dyDescent="0.35">
@@ -22263,7 +22269,7 @@
         <v>1581</v>
       </c>
       <c r="D1418" s="6" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1419" spans="2:4" x14ac:dyDescent="0.35">
@@ -22318,7 +22324,7 @@
         <v>1586</v>
       </c>
       <c r="D1423" s="6" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1424" spans="2:4" x14ac:dyDescent="0.35">
@@ -22373,7 +22379,7 @@
         <v>1591</v>
       </c>
       <c r="D1428" s="6" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1429" spans="2:4" x14ac:dyDescent="0.35">
@@ -22428,7 +22434,7 @@
         <v>628</v>
       </c>
       <c r="D1433" s="6" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1434" spans="2:4" x14ac:dyDescent="0.35">
@@ -22483,7 +22489,7 @@
         <v>1600</v>
       </c>
       <c r="D1438" s="6" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1439" spans="2:4" x14ac:dyDescent="0.35">
@@ -22538,7 +22544,7 @@
         <v>1605</v>
       </c>
       <c r="D1443" s="6" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1444" spans="2:4" x14ac:dyDescent="0.35">
@@ -22593,7 +22599,7 @@
         <v>1610</v>
       </c>
       <c r="D1448" s="6" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1449" spans="2:4" x14ac:dyDescent="0.35">
@@ -22648,7 +22654,7 @@
         <v>1615</v>
       </c>
       <c r="D1453" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1454" spans="2:4" x14ac:dyDescent="0.35">
@@ -22703,7 +22709,7 @@
         <v>1620</v>
       </c>
       <c r="D1458" s="6" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1459" spans="2:4" x14ac:dyDescent="0.35">
@@ -22758,7 +22764,7 @@
         <v>1625</v>
       </c>
       <c r="D1463" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1464" spans="2:4" x14ac:dyDescent="0.35">
@@ -22813,7 +22819,7 @@
         <v>1630</v>
       </c>
       <c r="D1468" s="6" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1469" spans="2:4" x14ac:dyDescent="0.35">
@@ -22868,7 +22874,7 @@
         <v>1635</v>
       </c>
       <c r="D1473" s="6" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1474" spans="2:4" x14ac:dyDescent="0.35">
@@ -22923,7 +22929,7 @@
         <v>1640</v>
       </c>
       <c r="D1478" s="6" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1479" spans="2:4" x14ac:dyDescent="0.35">
@@ -22978,7 +22984,7 @@
         <v>1645</v>
       </c>
       <c r="D1483" s="6" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1484" spans="2:4" x14ac:dyDescent="0.35">
@@ -23033,7 +23039,7 @@
         <v>1650</v>
       </c>
       <c r="D1488" s="6" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1489" spans="2:4" x14ac:dyDescent="0.35">
@@ -23088,7 +23094,7 @@
         <v>1655</v>
       </c>
       <c r="D1493" s="6" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1494" spans="2:4" x14ac:dyDescent="0.35">
@@ -23143,7 +23149,7 @@
         <v>1660</v>
       </c>
       <c r="D1498" s="6" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1499" spans="2:4" x14ac:dyDescent="0.35">
@@ -23198,7 +23204,7 @@
         <v>1665</v>
       </c>
       <c r="D1503" s="6" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1504" spans="2:4" x14ac:dyDescent="0.35">
@@ -23253,7 +23259,7 @@
         <v>1670</v>
       </c>
       <c r="D1508" s="6" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="1509" spans="2:4" x14ac:dyDescent="0.35">
@@ -23308,7 +23314,7 @@
         <v>1675</v>
       </c>
       <c r="D1513" s="6" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1514" spans="2:4" x14ac:dyDescent="0.35">
@@ -23363,7 +23369,7 @@
         <v>1680</v>
       </c>
       <c r="D1518" s="6" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1519" spans="2:4" x14ac:dyDescent="0.35">
@@ -23418,7 +23424,7 @@
         <v>1685</v>
       </c>
       <c r="D1523" s="6" t="s">
-        <v>1162</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1524" spans="2:4" x14ac:dyDescent="0.35">
@@ -23470,7 +23476,7 @@
         <v>1742</v>
       </c>
       <c r="D1528" s="6" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1529" spans="2:4" x14ac:dyDescent="0.35">
@@ -23510,7 +23516,7 @@
         <v>1747</v>
       </c>
       <c r="D1533" s="6" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1534" spans="2:4" x14ac:dyDescent="0.35">
@@ -23550,7 +23556,7 @@
         <v>1752</v>
       </c>
       <c r="D1538" s="6" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1539" spans="3:4" x14ac:dyDescent="0.35">
@@ -23590,7 +23596,7 @@
         <v>1757</v>
       </c>
       <c r="D1543" s="6" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1544" spans="3:4" x14ac:dyDescent="0.35">
@@ -23630,7 +23636,7 @@
         <v>1762</v>
       </c>
       <c r="D1548" s="6" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1549" spans="3:4" x14ac:dyDescent="0.35">
@@ -23670,7 +23676,7 @@
         <v>1766</v>
       </c>
       <c r="D1553" s="6" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1554" spans="3:4" x14ac:dyDescent="0.35">
@@ -23710,7 +23716,7 @@
         <v>1771</v>
       </c>
       <c r="D1558" s="6" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1559" spans="3:4" x14ac:dyDescent="0.35">
@@ -23750,7 +23756,7 @@
         <v>1776</v>
       </c>
       <c r="D1563" s="6" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1564" spans="3:4" x14ac:dyDescent="0.35">
@@ -23790,7 +23796,7 @@
         <v>1781</v>
       </c>
       <c r="D1568" s="6" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1569" spans="3:4" x14ac:dyDescent="0.35">
@@ -23830,7 +23836,7 @@
         <v>1786</v>
       </c>
       <c r="D1573" s="6" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1574" spans="3:4" x14ac:dyDescent="0.35">
@@ -23870,7 +23876,7 @@
         <v>1791</v>
       </c>
       <c r="D1578" s="6" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1579" spans="3:4" x14ac:dyDescent="0.35">
@@ -23910,7 +23916,7 @@
         <v>1796</v>
       </c>
       <c r="D1583" s="6" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1584" spans="3:4" x14ac:dyDescent="0.35">
@@ -23950,7 +23956,7 @@
         <v>1801</v>
       </c>
       <c r="D1588" s="6" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1589" spans="3:4" x14ac:dyDescent="0.35">
@@ -23990,7 +23996,7 @@
         <v>1806</v>
       </c>
       <c r="D1593" s="6" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1594" spans="3:4" x14ac:dyDescent="0.35">
@@ -24030,7 +24036,7 @@
         <v>1811</v>
       </c>
       <c r="D1598" s="6" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1599" spans="3:4" x14ac:dyDescent="0.35">
@@ -24070,7 +24076,7 @@
         <v>1816</v>
       </c>
       <c r="D1603" s="6" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1604" spans="3:4" x14ac:dyDescent="0.35">
@@ -24110,7 +24116,7 @@
         <v>1821</v>
       </c>
       <c r="D1608" s="6" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1609" spans="3:4" x14ac:dyDescent="0.35">
@@ -24150,7 +24156,7 @@
         <v>1826</v>
       </c>
       <c r="D1613" s="6" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1614" spans="3:4" x14ac:dyDescent="0.35">
@@ -24190,7 +24196,7 @@
         <v>1831</v>
       </c>
       <c r="D1618" s="6" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1619" spans="3:4" x14ac:dyDescent="0.35">
@@ -24230,7 +24236,7 @@
         <v>1836</v>
       </c>
       <c r="D1623" s="6" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1624" spans="3:4" x14ac:dyDescent="0.35">
@@ -24270,7 +24276,7 @@
         <v>1841</v>
       </c>
       <c r="D1628" s="6" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1629" spans="3:4" x14ac:dyDescent="0.35">
@@ -24310,7 +24316,7 @@
         <v>1846</v>
       </c>
       <c r="D1633" s="6" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1634" spans="3:4" x14ac:dyDescent="0.35">
@@ -24350,7 +24356,7 @@
         <v>1851</v>
       </c>
       <c r="D1638" s="6" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1639" spans="3:4" x14ac:dyDescent="0.35">
@@ -24390,7 +24396,7 @@
         <v>1856</v>
       </c>
       <c r="D1643" s="6" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1644" spans="3:4" x14ac:dyDescent="0.35">
@@ -24430,7 +24436,7 @@
         <v>1851</v>
       </c>
       <c r="D1648" s="6" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1649" spans="3:4" x14ac:dyDescent="0.35">
@@ -24470,7 +24476,7 @@
         <v>1861</v>
       </c>
       <c r="D1653" s="6" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1654" spans="3:4" x14ac:dyDescent="0.35">
@@ -24510,7 +24516,7 @@
         <v>1866</v>
       </c>
       <c r="D1658" s="6" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1659" spans="3:4" x14ac:dyDescent="0.35">
@@ -24550,7 +24556,7 @@
         <v>1871</v>
       </c>
       <c r="D1663" s="6" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1664" spans="3:4" x14ac:dyDescent="0.35">
@@ -24590,7 +24596,7 @@
         <v>1876</v>
       </c>
       <c r="D1668" s="6" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1669" spans="3:4" x14ac:dyDescent="0.35">
@@ -24630,7 +24636,7 @@
         <v>1881</v>
       </c>
       <c r="D1673" s="6" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1674" spans="3:4" x14ac:dyDescent="0.35">
@@ -24670,7 +24676,7 @@
         <v>1886</v>
       </c>
       <c r="D1678" s="6" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1679" spans="3:4" x14ac:dyDescent="0.35">
@@ -24710,7 +24716,7 @@
         <v>1891</v>
       </c>
       <c r="D1683" s="6" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1684" spans="3:4" x14ac:dyDescent="0.35">
@@ -24750,7 +24756,7 @@
         <v>1015</v>
       </c>
       <c r="D1688" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1689" spans="3:4" x14ac:dyDescent="0.35">
@@ -24790,7 +24796,7 @@
         <v>1900</v>
       </c>
       <c r="D1693" s="6" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1694" spans="3:4" x14ac:dyDescent="0.35">
@@ -24830,7 +24836,7 @@
         <v>1905</v>
       </c>
       <c r="D1698" s="6" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1699" spans="3:4" x14ac:dyDescent="0.35">
@@ -24870,7 +24876,7 @@
         <v>1910</v>
       </c>
       <c r="D1703" s="6" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1704" spans="3:4" x14ac:dyDescent="0.35">
@@ -24910,7 +24916,7 @@
         <v>1915</v>
       </c>
       <c r="D1708" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1709" spans="3:4" x14ac:dyDescent="0.35">
@@ -24950,7 +24956,7 @@
         <v>1920</v>
       </c>
       <c r="D1713" s="6" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1714" spans="3:4" x14ac:dyDescent="0.35">
@@ -24990,7 +24996,7 @@
         <v>1925</v>
       </c>
       <c r="D1718" s="6" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1719" spans="3:4" x14ac:dyDescent="0.35">
@@ -25030,7 +25036,7 @@
         <v>1930</v>
       </c>
       <c r="D1723" s="6" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1724" spans="3:4" x14ac:dyDescent="0.35">
@@ -25070,7 +25076,7 @@
         <v>1935</v>
       </c>
       <c r="D1728" s="6" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1729" spans="3:4" x14ac:dyDescent="0.35">
@@ -25110,7 +25116,7 @@
         <v>1940</v>
       </c>
       <c r="D1733" s="6" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1734" spans="3:4" x14ac:dyDescent="0.35">
@@ -25150,7 +25156,7 @@
         <v>1945</v>
       </c>
       <c r="D1738" s="6" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1739" spans="3:4" x14ac:dyDescent="0.35">
@@ -25190,7 +25196,7 @@
         <v>1950</v>
       </c>
       <c r="D1743" s="6" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1744" spans="3:4" x14ac:dyDescent="0.35">
@@ -25230,7 +25236,7 @@
         <v>1955</v>
       </c>
       <c r="D1748" s="6" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1749" spans="3:4" x14ac:dyDescent="0.35">
@@ -25270,7 +25276,7 @@
         <v>1960</v>
       </c>
       <c r="D1753" s="6" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1754" spans="3:4" x14ac:dyDescent="0.35">
@@ -25310,7 +25316,7 @@
         <v>1965</v>
       </c>
       <c r="D1758" s="6" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1759" spans="3:4" x14ac:dyDescent="0.35">
@@ -25350,7 +25356,7 @@
         <v>1970</v>
       </c>
       <c r="D1763" s="6" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1764" spans="3:4" x14ac:dyDescent="0.35">
@@ -25390,7 +25396,7 @@
         <v>1975</v>
       </c>
       <c r="D1768" s="6" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1769" spans="3:4" x14ac:dyDescent="0.35">
@@ -25430,7 +25436,7 @@
         <v>1980</v>
       </c>
       <c r="D1773" s="6" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1774" spans="3:4" x14ac:dyDescent="0.35">
@@ -25470,7 +25476,7 @@
         <v>1985</v>
       </c>
       <c r="D1778" s="6" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1779" spans="3:4" x14ac:dyDescent="0.35">
@@ -25510,7 +25516,7 @@
         <v>1990</v>
       </c>
       <c r="D1783" s="6" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1784" spans="3:4" x14ac:dyDescent="0.35">
